--- a/translations Dance2Dance Ultima versao.xlsx
+++ b/translations Dance2Dance Ultima versao.xlsx
@@ -24452,11 +24452,11 @@
         <is>
           <t>Dançar é também encontrar o outro.
  Há músicas que nos fazem viajar, ritmos que despertam o corpo e movimentos que nos aproximam, mesmo quando não falamos a mesma língua.
- Be The Dance Day é um encontro aberto a todos, para dançar, divertir-se e partilhar a experiência do movimento ao som de diferentes músicas e culturas.
+ Be the Dance Day é um encontro aberto a todos, para dançar, divertir-se e partilhar a experiência do movimento ao som de diferentes músicas e culturas.
  Ao longo do encontro, somos convidados a experimentar diferentes ritmos, formas de dançar e maneiras de nos relacionarmos com a música e com quem está à nossa volta. Sem necessidade de saber dançar, sem passos certos ou errados, apenas a curiosidade de experimentar e a liberdade de nos deixarmos levar.
  Mais do que aprender uma dança, é uma oportunidade para viver a dança como encontro: com a música, com o corpo, com diferentes culturas e com outras pessoas.
  ​
- Be The Dance Day é uma celebração do movimento e da diversidade. Um espaço para soltar o corpo, descobrir novos ritmos, se divertir, criar conexões e simplesmente dançar.
+ Be the Dance Day é uma celebração do movimento e da diversidade. Um espaço para soltar o corpo, descobrir novos ritmos, se divertir, criar conexões e simplesmente dançar.
  Venha como você é. Vamos dançar juntos.</t>
         </is>
       </c>
@@ -24464,11 +24464,11 @@
         <is>
           <t>Dancing is also encountering the other.
 There is music that makes us travel, rhythms that awaken the body, and movements that bring us closer, even when we don't speak the same language.
-Be The Dance Day is an open gathering for everyone to dance, have fun, and share the experience of movement to the sounds of different music and cultures.
+Be the Dance Day is an open gathering for everyone to dance, have fun, and share the experience of movement to the sounds of different music and cultures.
 Throughout the gathering, we are invited to experience different rhythms, ways of dancing, and ways of relating to music and those around us. No dance experience is necessary, no right or wrong steps, just the curiosity to experiment and the freedom to let ourselves go.
 More than learning a dance, it is an opportunity to experience dance as an encounter: with music, with the body, with different cultures, and with other people.
 ​
-Be The Dance Day is a celebration of movement and diversity. A space to let the body loose, discover new rhythms, have fun, create connections, and simply dance.
+Be the Dance Day is a celebration of movement and diversity. A space to let the body loose, discover new rhythms, have fun, create connections, and simply dance.
 Come as you are. Let's dance together.</t>
         </is>
       </c>
@@ -24476,11 +24476,11 @@
         <is>
           <t>Å danse er også å møte den andre.
 Det finnes musikk som får oss til å reise, rytmer som vekker kroppen, og bevegelser som bringer oss nærmere hverandre, selv når vi ikke snakker samme språk.
-Be The Dance Day er en åpen samling for alle, for å danse, ha det gøy og dele opplevelsen av bevegelse til lyden av forskjellig musikk og kulturer.
+Be the Dance Day er en åpen samling for alle, for å danse, ha det gøy og dele opplevelsen av bevegelse til lyden av forskjellig musikk og kulturer.
 Gjennom samlingen inviteres vi til å oppleve ulike rytmer, måter å danse på, og måter å forholde oss til musikken og de rundt oss. Ingen danseerfaring er nødvendig, ingen riktige eller gale trinn, bare nysgjerrigheten til å eksperimentere og friheten til å la oss rive med.
 Mer enn å lære en dans, er det en mulighet til å oppleve dans som et møte: med musikk, med kroppen, med forskjellige kulturer, og med andre mennesker.
 ​
-Be The Dance Day er en feiring av bevegelse og mangfold. Et rom for å la kroppen delta, oppdage nye rytmer, ha det gøy, skape forbindelser, og rett og slett danse.
+Be the Dance Day er en feiring av bevegelse og mangfold. Et rom for å la kroppen delta, oppdage nye rytmer, ha det gøy, skape forbindelser, og rett og slett danse.
 Kom som du er. La oss danse sammen.</t>
         </is>
       </c>
@@ -24543,17 +24543,17 @@
       </c>
       <c r="D660" s="18" t="inlineStr">
         <is>
-          <t>BE THE DANCE DAY</t>
+          <t>Be the Dance Day</t>
         </is>
       </c>
       <c r="E660" s="18" t="inlineStr">
         <is>
-          <t>BE THE DANCE DAY</t>
+          <t>Be the Dance Day</t>
         </is>
       </c>
       <c r="F660" s="18" t="inlineStr">
         <is>
-          <t>BE THE DANCE DAY</t>
+          <t>Be the Dance Day</t>
         </is>
       </c>
       <c r="G660" s="5" t="inlineStr">
@@ -24584,10 +24584,10 @@
  O que é presença?
  Neste workshop, investigamos esse “algo mais”. Um convite para ir além da execução, do intelecto e da mente que observa e controla, e mergulhar numa experiência de presença, consciência e entrega.
  Através de práticas de educação somática, meditação, improvisação guiada e outras ferramentas de exploração do movimento, criamos espaço para escutar o corpo, ampliar a percepção e descobrir novas possibilidades de estar em cena.
- Mais do que acrescentar novas ferramentas à técnica, Be The Dance Pro propõe uma jornada para dentro de si. Uma investigação sobre o que acontece quando deixamos de apenas fazer a dança e permitimos que ela aconteça através de nós.
+ Mais do que acrescentar novas ferramentas à técnica, Be the Dance Pro propõe uma jornada para dentro de si. Uma investigação sobre o que acontece quando deixamos de apenas fazer a dança e permitimos que ela aconteça através de nós.
  O que é carisma?
  ​
- Be The Dance Pro é uma experiência de presença e totalidade. Um espaço para aprofundar a relação entre corpo, mente e movimento e descobrir aquilo que torna cada bailarino único. Uma busca por se perder na dança para encontrar aquele lugar onde bailarino e dança deixam de ser duas coisas diferentes.
+ Be the Dance Pro é uma experiência de presença e totalidade. Um espaço para aprofundar a relação entre corpo, mente e movimento e descobrir aquilo que torna cada bailarino único. Uma busca por se perder na dança para encontrar aquele lugar onde bailarino e dança deixam de ser duas coisas diferentes.
  O momento em que o bailarino é a própria dança.</t>
         </is>
       </c>
@@ -24598,10 +24598,10 @@
 What is presence?
 In this workshop, we investigate this “something more”. An invitation to go beyond execution, the intellect, and the mind that observes and controls, and dive into an experience of presence, awareness, and surrender.
 Through practices of somatic education, meditation, guided improvisation, and other tools for movement exploration, we create space to listen to the body, expand perception, and discover new possibilities of being on stage.
-More than adding new tools to technique, Be The Dance Pro proposes a journey inward. An investigation into what happens when we stop merely doing the dance and allow it to happen through us.
+More than adding new tools to technique, Be the Dance Pro proposes a journey inward. An investigation into what happens when we stop merely doing the dance and allow it to happen through us.
 What is charisma?
 ​
-Be The Dance Pro is an experience of presence and totality. A space to deepen the relationship between body, mind, and movement and discover what makes each dancer unique. A quest to lose oneself in the dance to find that place where dancer and dance cease to be two different things.
+Be the Dance Pro is an experience of presence and totality. A space to deepen the relationship between body, mind, and movement and discover what makes each dancer unique. A quest to lose oneself in the dance to find that place where dancer and dance cease to be two different things.
 The moment the dancer is the dance itself.</t>
         </is>
       </c>
@@ -24612,10 +24612,10 @@
 Hva er tilstedeværelse?
 I denne workshopen undersøker vi dette «noe mer». En invitasjon til å gå utover utførelse, intellektet og sinnet som observerer og kontrollerer, og dykke ned i en opplevelse av tilstedeværelse, bevissthet og overgivelse.
 Gjennom praksiser innen somatisk utdanning, meditasjon, veiledet improvisasjon og andre verktøy for bevegelsesutforskning, skaper vi rom for å lytte til kroppen, utvide persepsjonen og oppdage nye muligheter for å være på scenen.
-Mer enn å legge til nye verktøy til teknikken, foreslår Be The Dance Pro en reise innover. En undersøkelse av hva som skjer når vi slutter å bare gjøre dansen og lar den skje gjennom oss.
+Mer enn å legge til nye verktøy til teknikken, foreslår Be the Dance Pro en reise innover. En undersøkelse av hva som skjer når vi slutter å bare gjøre dansen og lar den skje gjennom oss.
 Hva er karisma?
 ​
-Be The Dance Pro er en opplevelse av tilstedeværelse og totalitet. Et rom for å utdype forholdet mellom kropp, sinn og bevegelse og oppdage hva som gjør hver danser unik. En søken etter å miste seg selv i dansen for å finne det stedet hvor danser og dans slutter å være to forskjellige ting.
+Be the Dance Pro er en opplevelse av tilstedeværelse og totalitet. Et rom for å utdype forholdet mellom kropp, sinn og bevegelse og oppdage hva som gjør hver danser unik. En søken etter å miste seg selv i dansen for å finne det stedet hvor danser og dans slutter å være to forskjellige ting.
 Øyeblikket hvor danseren er selve dansen.</t>
         </is>
       </c>
@@ -24678,17 +24678,17 @@
       </c>
       <c r="D663" s="19" t="inlineStr">
         <is>
-          <t>BE THE DANCE PRO</t>
+          <t>Be the Dance Pro</t>
         </is>
       </c>
       <c r="E663" s="19" t="inlineStr">
         <is>
-          <t>BE THE DANCE PRO</t>
+          <t>Be the Dance Pro</t>
         </is>
       </c>
       <c r="F663" s="19" t="inlineStr">
         <is>
-          <t>BE THE DANCE PRO</t>
+          <t>Be the Dance Pro</t>
         </is>
       </c>
       <c r="G663" s="9" t="inlineStr">

--- a/translations Dance2Dance Ultima versao.xlsx
+++ b/translations Dance2Dance Ultima versao.xlsx
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -204,6 +204,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -484,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H1059"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1119,7 +1122,7 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>Community projects that reach across streets and neighborhoods—weaving connections, building bonds, and sparking transformation.</t>
+          <t>Community projects that reach across streets and neighborhoods - weaving connections, building bonds, and sparking transformation.</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -11319,7 +11322,7 @@
       </c>
       <c r="E299" s="19" t="inlineStr">
         <is>
-          <t>Biostretch uses the most accessible tool you have—your attention—to transform how your body organizes itself.</t>
+          <t>Biostretch uses the most accessible tool you have - your attention - to transform how your body organizes itself.</t>
         </is>
       </c>
       <c r="F299" s="19" t="inlineStr">
@@ -11575,12 +11578,12 @@
       </c>
       <c r="E306" s="18" t="inlineStr">
         <is>
-          <t>Automatic habits of movement — which were never chosen — become visible for the first time.</t>
+          <t>Automatic habits of movement: which were never chosen: become visible for the first time.</t>
         </is>
       </c>
       <c r="F306" s="18" t="inlineStr">
         <is>
-          <t>Automatiske bevegelsesvaner — som aldri ble valgt — blir synlige for første gang.</t>
+          <t>Automatiske bevegelsesvaner: som aldri ble valgt: blir synlige for første gang.</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -17651,7 +17654,7 @@
       </c>
       <c r="E474" s="18" t="inlineStr">
         <is>
-          <t>Every company has its own dynamics. Every team faces different physical and mental challenges throughout the workday. Long hours at the computer, repetitive tasks, many hours standing, pressure for results, and an intense routine can generate wear and tear, and accumulated tension that goes unnoticed—until the body sends its signals.</t>
+          <t>Every company has its own dynamics. Every team faces different physical and mental challenges throughout the workday. Long hours at the computer, repetitive tasks, many hours standing, pressure for results, and an intense routine can generate wear and tear, and accumulated tension that goes unnoticed - until the body sends its signals.</t>
         </is>
       </c>
       <c r="F474" s="18" t="inlineStr">
@@ -30652,17 +30655,17 @@
       </c>
       <c r="D823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo é um bairro de contrastes — diversidade, história e riqueza cultural convivem com desigualdades de acesso a serviços e atividades de qualidade. É exatamente esse contexto que nos chama a agir.</t>
+          <t>Gamle Oslo é um bairro de contrastes: diversidade, história e riqueza cultural convivem com desigualdades de acesso a serviços e atividades de qualidade. É exatamente esse contexto que nos chama a agir.</t>
         </is>
       </c>
       <c r="E823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo is a neighbourhood of contrasts — diversity, history and cultural richness coexist with inequalities in access to quality services and activities. This is exactly the context that calls us to act.</t>
+          <t>Gamle Oslo is a neighbourhood of contrasts: diversity, history and cultural richness coexist with inequalities in access to quality services and activities. This is exactly the context that calls us to act.</t>
         </is>
       </c>
       <c r="F823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo er et nabolag fylt av kontraster — mangfold, historie og kulturell rikdom eksisterer side om side med ulikhet i tilgang til kvalitetstjenester og aktiviteter. Det er nettopp denne virkeligheten som kaller oss til handling.</t>
+          <t>Gamle Oslo er et nabolag fylt av kontraster: mangfold, historie og kulturell rikdom eksisterer side om side med ulikhet i tilgang til kvalitetstjenester og aktiviteter. Det er nettopp denne virkeligheten som kaller oss til handling.</t>
         </is>
       </c>
       <c r="G823" s="9" t="inlineStr">
@@ -30692,17 +30695,17 @@
       </c>
       <c r="D824" s="18" t="inlineStr">
         <is>
-          <t>O Dance2Dance nasce nesse território com uma missão clara: que a dança, a expressão corporal e o bem-estar não sejam privilégio de quem pode pagar. Cada workshop que desenvolvemos tem a mesma qualidade, o mesmo cuidado e a mesma intenção — independentemente de quem está na sala.</t>
+          <t>O Dance2Dance nasce nesse território com uma missão clara: que a dança, a expressão corporal e o bem-estar não sejam privilégio de quem pode pagar. Cada workshop que desenvolvemos tem a mesma qualidade, o mesmo cuidado e a mesma intenção: independentemente de quem está na sala.</t>
         </is>
       </c>
       <c r="E824" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance is born in this territory with a clear mission: that dance, movement and well-being should not be a privilege for those who can pay. Every workshop we develop carries the same quality, the same care and the same intention — regardless of who is in the room.</t>
+          <t>Dance2Dance is born in this territory with a clear mission: that dance, movement and well-being should not be a privilege for those who can pay. Every workshop we develop carries the same quality, the same care and the same intention: regardless of who is in the room.</t>
         </is>
       </c>
       <c r="F824" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance fødes i dette territoriet med et tydelig oppdrag: at dans, kroppsuttrykk og velvære ikke skal være et privilegium for dem som kan betale. Hver workshop vi utvikler har samme kvalitet, samme omsorg og samme intensjon — uavhengig av hvem som er i rommet.</t>
+          <t>Dance2Dance fødes i dette territoriet med et tydelig oppdrag: at dans, kroppsuttrykk og velvære ikke skal være et privilegium for dem som kan betale. Hver workshop vi utvikler har samme kvalitet, samme omsorg og samme intensjon: uavhengig av hvem som er i rommet.</t>
         </is>
       </c>
       <c r="G824" s="5" t="inlineStr">
@@ -30876,17 +30879,17 @@
       </c>
       <c r="D829" s="19" t="inlineStr">
         <is>
-          <t>Fundos, empresas e parceiros que chegam agora são parte da fundação — e da história — deste projeto. Entre em contato e descubra como fazer parte.</t>
+          <t>Fundos, empresas e parceiros que chegam agora são parte da fundação: e da história: deste projeto. Entre em contato e descubra como fazer parte.</t>
         </is>
       </c>
       <c r="E829" s="19" t="inlineStr">
         <is>
-          <t>Funds, companies and partners who arrive now are part of the foundation — and the story — of this project. Get in touch and discover how to be part of it.</t>
+          <t>Funds, companies and partners who arrive now are part of the foundation: and the story: of this project. Get in touch and discover how to be part of it.</t>
         </is>
       </c>
       <c r="F829" s="19" t="inlineStr">
         <is>
-          <t>Fond, bedrifter og partnere som kommer nå er en del av grunnlaget — og historien — til dette prosjektet. Ta kontakt og finn ut hvordan du kan være en del av det.</t>
+          <t>Fond, bedrifter og partnere som kommer nå er en del av grunnlaget: og historien: til dette prosjektet. Ta kontakt og finn ut hvordan du kan være en del av det.</t>
         </is>
       </c>
       <c r="G829" s="9" t="inlineStr">
@@ -31056,17 +31059,17 @@
       </c>
       <c r="D834" s="18" t="inlineStr">
         <is>
-          <t>Um modelo de acesso universal à cultura e ao movimento. Workshops de alto nível, gratuitos para moradores de Gamle Oslo — sustentados por múltiplas fontes de financiamento.</t>
+          <t>Um modelo de acesso universal à cultura e ao movimento. Workshops de alto nível, gratuitos para moradores de Gamle Oslo: sustentados por múltiplas fontes de financiamento.</t>
         </is>
       </c>
       <c r="E834" s="18" t="inlineStr">
         <is>
-          <t>A model for universal access to culture and movement. Premium workshops, free for residents of Gamle Oslo — sustained by multiple funding sources.</t>
+          <t>A model for universal access to culture and movement. Premium workshops, free for residents of Gamle Oslo: sustained by multiple funding sources.</t>
         </is>
       </c>
       <c r="F834" s="18" t="inlineStr">
         <is>
-          <t>En modell for universell tilgang til kultur og bevegelse. Premium workshops, gratis for beboere i Gamle Oslo — båret av flere finansieringskilder.</t>
+          <t>En modell for universell tilgang til kultur og bevegelse. Premium workshops, gratis for beboere i Gamle Oslo: båret av flere finansieringskilder.</t>
         </is>
       </c>
       <c r="G834" s="5" t="inlineStr">
@@ -31204,17 +31207,17 @@
       </c>
       <c r="D838" s="18" t="inlineStr">
         <is>
-          <t>O Dance2Dance foi desenhado para não depender de uma única fonte. Nossa sustentabilidade nasce da combinação estratégica de múltiplos pilares — cada um essencial, nenhum suficiente sozinho.</t>
+          <t>O Dance2Dance foi desenhado para não depender de uma única fonte. Nossa sustentabilidade nasce da combinação estratégica de múltiplos pilares: cada um essencial, nenhum suficiente sozinho.</t>
         </is>
       </c>
       <c r="E838" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance was designed not to rely on a single source. Our sustainability comes from the strategic combination of multiple pillars — each essential, none sufficient alone.</t>
+          <t>Dance2Dance was designed not to rely on a single source. Our sustainability comes from the strategic combination of multiple pillars: each essential, none sufficient alone.</t>
         </is>
       </c>
       <c r="F838" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance er designet for å ikke stole på en enkelt kilde. Vår bærekraft kommer fra den strategiske kombinasjonen av flere pilarer — hver enkelt essensiell, ingen tilstrekkelig alene.</t>
+          <t>Dance2Dance er designet for å ikke stole på en enkelt kilde. Vår bærekraft kommer fra den strategiske kombinasjonen av flere pilarer: hver enkelt essensiell, ingen tilstrekkelig alene.</t>
         </is>
       </c>
       <c r="G838" s="5" t="inlineStr">
@@ -31856,17 +31859,17 @@
       </c>
       <c r="D856" s="18" t="inlineStr">
         <is>
-          <t>“O acesso gratuito com transparência de preço cria dignidade. A pessoa não recebe caridade — recebe a oportunidade de participar de algo que tem valor real.”</t>
+          <t>“O acesso gratuito com transparência de preço cria dignidade. A pessoa não recebe caridade: recebe a oportunidade de participar de algo que tem valor real.”</t>
         </is>
       </c>
       <c r="E856" s="18" t="inlineStr">
         <is>
-          <t>“Free access with price transparency creates dignity. The person is not receiving charity — they are receiving the opportunity to be part of something with real value.”</t>
+          <t>“Free access with price transparency creates dignity. The person is not receiving charity: they are receiving the opportunity to be part of something with real value.”</t>
         </is>
       </c>
       <c r="F856" s="18" t="inlineStr">
         <is>
-          <t>“Gratis tilgang med pristransparens skaper verdighet. Personen mottar ikke veldedighet — de mottar muligheten til å være en del av noe med ekte verdi.”</t>
+          <t>“Gratis tilgang med pristransparens skaper verdighet. Personen mottar ikke veldedighet: de mottar muligheten til å være en del av noe med ekte verdi.”</t>
         </is>
       </c>
       <c r="G856" s="5" t="inlineStr">
@@ -32036,17 +32039,17 @@
       </c>
       <c r="D861" s="19" t="inlineStr">
         <is>
-          <t>Quem recebe gratuitamente recebe exatamente o mesmo que quem paga. Tornamos o preço real visível porque valor percebido importa — tanto para quem apia quanto para quem participa.</t>
+          <t>Quem recebe gratuitamente recebe exatamente o mesmo que quem paga. Tornamos o preço real visível porque valor percebido importa: tanto para quem apia quanto para quem participa.</t>
         </is>
       </c>
       <c r="E861" s="19" t="inlineStr">
         <is>
-          <t>Those who receive it for free receive exactly the same as those who pay. We make the real price visible because perceived value matters — for supporters and participants alike.</t>
+          <t>Those who receive it for free receive exactly the same as those who pay. We make the real price visible because perceived value matters: for supporters and participants alike.</t>
         </is>
       </c>
       <c r="F861" s="19" t="inlineStr">
         <is>
-          <t>De som mottar det gratis, mottar nøyaktig det samme som de som betaler. Vi gjør den reelle prisen synlig fordi opplevd verdi betyr noe — både for støttespillere og deltakere.</t>
+          <t>De som mottar det gratis, mottar nøyaktig det samme som de som betaler. Vi gjør den reelle prisen synlig fordi opplevd verdi betyr noe: både for støttespillere og deltakere.</t>
         </is>
       </c>
       <c r="G861" s="9" t="inlineStr">
@@ -36297,108 +36300,3404 @@
       </c>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="15" t="n"/>
-      <c r="B975" s="16" t="n"/>
+      <c r="A975" s="15" t="n">
+        <v>974</v>
+      </c>
+      <c r="B975" s="16" t="inlineStr">
+        <is>
+          <t>nav</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>nav.pricing</t>
+        </is>
+      </c>
+      <c r="D975" s="22" t="inlineStr">
+        <is>
+          <t>Valores &amp; Acesso</t>
+        </is>
+      </c>
+      <c r="E975" s="22" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Access</t>
+        </is>
+      </c>
+      <c r="F975" s="22" t="inlineStr">
+        <is>
+          <t>Priser &amp; Tilgang</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H975" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Standard navigation label reflecting fair rates and community access]</t>
+        </is>
+      </c>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="15" t="n"/>
-      <c r="B976" s="16" t="n"/>
+      <c r="A976" s="15" t="n">
+        <v>975</v>
+      </c>
+      <c r="B976" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>scholarshipModal.badge</t>
+        </is>
+      </c>
+      <c r="D976" s="22" t="inlineStr">
+        <is>
+          <t>Tøyen &amp; Grønland • Acesso Comunitário</t>
+        </is>
+      </c>
+      <c r="E976" s="22" t="inlineStr">
+        <is>
+          <t>Tøyen &amp; Grønland • Community Access</t>
+        </is>
+      </c>
+      <c r="F976" s="22" t="inlineStr">
+        <is>
+          <t>Tøyen &amp; Grønland • Lokalt Stipend</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H976" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Dignified community badge for eligible Oslo neighborhoods]</t>
+        </is>
+      </c>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="15" t="n"/>
-      <c r="B977" s="16" t="n"/>
+      <c r="A977" s="15" t="n">
+        <v>976</v>
+      </c>
+      <c r="B977" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>scholarshipModal.question</t>
+        </is>
+      </c>
+      <c r="D977" s="22" t="inlineStr">
+        <is>
+          <t>Você deseja solicitar bolsa integral para esse workshop?</t>
+        </is>
+      </c>
+      <c r="E977" s="22" t="inlineStr">
+        <is>
+          <t>Would you like to request a full scholarship for this workshop?</t>
+        </is>
+      </c>
+      <c r="F977" s="22" t="inlineStr">
+        <is>
+          <t>Ønsker du å søke om fullt stipend til denne workshopen?</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H977" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'til denne workshopen' is natural Norwegian preposition for course application]</t>
+        </is>
+      </c>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="15" t="n"/>
-      <c r="B978" s="16" t="n"/>
+      <c r="A978" s="15" t="n">
+        <v>977</v>
+      </c>
+      <c r="B978" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>scholarshipModal.description</t>
+        </is>
+      </c>
+      <c r="D978" s="22" t="inlineStr">
+        <is>
+          <t>Identificamos que seu endereço registrado é em {{neighborhood}}. Moradores de Tøyen e Grønland têm direito a bolsas de 100% financiadas pelo nosso ecossistema social de sustentabilidade.</t>
+        </is>
+      </c>
+      <c r="E978" s="22" t="inlineStr">
+        <is>
+          <t>We noticed that your registered address is in {{neighborhood}}. Residents of Tøyen and Grønland are eligible for 100% full scholarships funded through our social sustainability model.</t>
+        </is>
+      </c>
+      <c r="F978" s="22" t="inlineStr">
+        <is>
+          <t>Vi ser at din registrerte adresse er {{neighborhood}}. Beboere på Tøyen og Grønland har rett til 100 % fullt stipend finansiert gjennom vår sosiale bærekraftsmodell.</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H978" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Warm, welcoming phrasing avoiding robotic terms; natural Oslo idiom 'på Tøyen og Grønland']</t>
+        </is>
+      </c>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="15" t="n"/>
-      <c r="B979" s="16" t="n"/>
+      <c r="A979" s="15" t="n">
+        <v>978</v>
+      </c>
+      <c r="B979" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>scholarshipModal.solidarityNote</t>
+        </is>
+      </c>
+      <c r="D979" s="22" t="inlineStr">
+        <is>
+          <t>Se você tem condições financeiras de investir no valor da vaga, sua taxa ajuda a manter essa oportunidade aberta para quem mais precisa.</t>
+        </is>
+      </c>
+      <c r="E979" s="22" t="inlineStr">
+        <is>
+          <t>If you have the financial means to pay the standard tuition, your contribution helps keep this opportunity open for those who need it most.</t>
+        </is>
+      </c>
+      <c r="F979" s="22" t="inlineStr">
+        <is>
+          <t>Dersom du har økonomisk mulighet til å betale ordinær kursavgift, bidrar du til å holde denne ordningen åpen for dem som trenger det mest.</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H979" s="22" t="inlineStr">
+        <is>
+          <t>[NO: Replaced awkward repetition 'bidrar ditt bidrag' with fluent native structure]</t>
+        </is>
+      </c>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="15" t="n"/>
-      <c r="B980" s="16" t="n"/>
+      <c r="A980" s="15" t="n">
+        <v>979</v>
+      </c>
+      <c r="B980" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>scholarshipModal.declineBtn</t>
+        </is>
+      </c>
+      <c r="D980" s="22" t="inlineStr">
+        <is>
+          <t>Não, tenho condições de pagar</t>
+        </is>
+      </c>
+      <c r="E980" s="22" t="inlineStr">
+        <is>
+          <t>No, I have the means to pay</t>
+        </is>
+      </c>
+      <c r="F980" s="22" t="inlineStr">
+        <is>
+          <t>Nei, jeg har mulighet til å betale</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H980" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Direct and polite response choice]</t>
+        </is>
+      </c>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="15" t="n"/>
-      <c r="B981" s="16" t="n"/>
+      <c r="A981" s="15" t="n">
+        <v>980</v>
+      </c>
+      <c r="B981" s="16" t="inlineStr">
+        <is>
+          <t>scholarshipModal</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>scholarshipModal.confirmBtn</t>
+        </is>
+      </c>
+      <c r="D981" s="22" t="inlineStr">
+        <is>
+          <t>Sim, solicito bolsa integral</t>
+        </is>
+      </c>
+      <c r="E981" s="22" t="inlineStr">
+        <is>
+          <t>Yes, I request a full scholarship</t>
+        </is>
+      </c>
+      <c r="F981" s="22" t="inlineStr">
+        <is>
+          <t>Ja, jeg søker om fullt stipend</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H981" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Clear, dignified scholarship request]</t>
+        </is>
+      </c>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="15" t="n"/>
-      <c r="B982" s="16" t="n"/>
+      <c r="A982" s="15" t="n">
+        <v>981</v>
+      </c>
+      <c r="B982" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>pricingPage.seoTitle</t>
+        </is>
+      </c>
+      <c r="D982" s="22" t="inlineStr">
+        <is>
+          <t>Valores &amp; Acesso</t>
+        </is>
+      </c>
+      <c r="E982" s="22" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Access</t>
+        </is>
+      </c>
+      <c r="F982" s="22" t="inlineStr">
+        <is>
+          <t>Priser &amp; Tilgang</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H982" s="22" t="inlineStr">
+        <is>
+          <t>[SEO title tag]</t>
+        </is>
+      </c>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="15" t="n"/>
-      <c r="B983" s="16" t="n"/>
+      <c r="A983" s="15" t="n">
+        <v>982</v>
+      </c>
+      <c r="B983" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>pricingPage.seoDesc</t>
+        </is>
+      </c>
+      <c r="D983" s="22" t="inlineStr">
+        <is>
+          <t>Transparência financeira e acesso comunitário. Conheça nossos valores por workshop e o programa de bolsas integrais para Tøyen e Grønland.</t>
+        </is>
+      </c>
+      <c r="E983" s="22" t="inlineStr">
+        <is>
+          <t>Financial transparency and community access. Explore our workshop rates and 100% full scholarship program for Tøyen and Grønland.</t>
+        </is>
+      </c>
+      <c r="F983" s="22" t="inlineStr">
+        <is>
+          <t>Økonomisk åpenhet og samfunnsdeltakelse. Se kursoversikt, priser og vårt program for 100 % fullt stipend for beboere på Tøyen og Grønland.</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H983" s="22" t="inlineStr">
+        <is>
+          <t>[SEO meta description]</t>
+        </is>
+      </c>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="15" t="n"/>
-      <c r="B984" s="16" t="n"/>
+      <c r="A984" s="15" t="n">
+        <v>983</v>
+      </c>
+      <c r="B984" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>pricingPage.hero.kicker</t>
+        </is>
+      </c>
+      <c r="D984" s="22" t="inlineStr">
+        <is>
+          <t>Sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="E984" s="22" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F984" s="22" t="inlineStr">
+        <is>
+          <t>Ideell Organisasjon</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H984" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'Ideell Organisasjon' is the precise Norwegian legal/social term]</t>
+        </is>
+      </c>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="15" t="n"/>
-      <c r="B985" s="16" t="n"/>
+      <c r="A985" s="15" t="n">
+        <v>984</v>
+      </c>
+      <c r="B985" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>pricingPage.hero.title</t>
+        </is>
+      </c>
+      <c r="D985" s="22" t="inlineStr">
+        <is>
+          <t>Valores &amp; Acesso</t>
+        </is>
+      </c>
+      <c r="E985" s="22" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Access</t>
+        </is>
+      </c>
+      <c r="F985" s="22" t="inlineStr">
+        <is>
+          <t>Priser &amp; Tilgang</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H985" s="22" t="inlineStr">
+        <is>
+          <t>[Page primary headline]</t>
+        </is>
+      </c>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="15" t="n"/>
-      <c r="B986" s="16" t="n"/>
+      <c r="A986" s="15" t="n">
+        <v>985</v>
+      </c>
+      <c r="B986" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>pricingPage.hero.subtitle</t>
+        </is>
+      </c>
+      <c r="D986" s="22" t="inlineStr">
+        <is>
+          <t>é uma organização social sem fins lucrativos sediada em Oslo. Nossos valores são estruturados em um modelo de solidariedade: a receita gerada por quem pode investir viabiliza o acesso integral e gratuito para a comunidade local.</t>
+        </is>
+      </c>
+      <c r="E986" s="22" t="inlineStr">
+        <is>
+          <t>is a non-profit social organization based in Oslo. Our financial model is rooted in solidarity: fees from those who can invest directly fund full, free access for our local community.</t>
+        </is>
+      </c>
+      <c r="F986" s="22" t="inlineStr">
+        <is>
+          <t>er en ideell organisasjon med base i Oslo. Vår økonomiske modell er forankret i solidaritet: kursavgiften fra dem som har mulighet til å investere, muliggjør full og gratis deltakelse for lokalmiljøet.</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H986" s="22" t="inlineStr">
+        <is>
+          <t>[EN/NO: Native rhetorical phrasing 'rooted in solidarity' / 'forankret i solidaritet']</t>
+        </is>
+      </c>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="15" t="n"/>
-      <c r="B987" s="16" t="n"/>
+      <c r="A987" s="15" t="n">
+        <v>986</v>
+      </c>
+      <c r="B987" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.kicker</t>
+        </is>
+      </c>
+      <c r="D987" s="22" t="inlineStr">
+        <is>
+          <t>Sustentabilidade Consciente</t>
+        </is>
+      </c>
+      <c r="E987" s="22" t="inlineStr">
+        <is>
+          <t>Conscious Sustainability</t>
+        </is>
+      </c>
+      <c r="F987" s="22" t="inlineStr">
+        <is>
+          <t>Bærekraftig Fellesskap</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H987" s="22" t="inlineStr">
+        <is>
+          <t>[Category kicker]</t>
+        </is>
+      </c>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="15" t="n"/>
-      <c r="B988" s="16" t="n"/>
+      <c r="A988" s="15" t="n">
+        <v>987</v>
+      </c>
+      <c r="B988" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.title</t>
+        </is>
+      </c>
+      <c r="D988" s="22" t="inlineStr">
+        <is>
+          <t>Valores Justos de Mercado</t>
+        </is>
+      </c>
+      <c r="E988" s="22" t="inlineStr">
+        <is>
+          <t>Fair Market Rates</t>
+        </is>
+      </c>
+      <c r="F988" s="22" t="inlineStr">
+        <is>
+          <t>Rettferdig Markedspris</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H988" s="22" t="inlineStr">
+        <is>
+          <t>[Standard economic phrasing in both languages]</t>
+        </is>
+      </c>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="15" t="n"/>
-      <c r="B989" s="16" t="n"/>
+      <c r="A989" s="15" t="n">
+        <v>988</v>
+      </c>
+      <c r="B989" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.subtitle</t>
+        </is>
+      </c>
+      <c r="D989" s="22" t="inlineStr">
+        <is>
+          <t>Para quem participa investindo</t>
+        </is>
+      </c>
+      <c r="E989" s="22" t="inlineStr">
+        <is>
+          <t>For those who invest in participation</t>
+        </is>
+      </c>
+      <c r="F989" s="22" t="inlineStr">
+        <is>
+          <t>For deg som investerer</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H989" s="22" t="inlineStr">
+        <is>
+          <t>[Audience subtitle]</t>
+        </is>
+      </c>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="15" t="n"/>
-      <c r="B990" s="16" t="n"/>
+      <c r="A990" s="15" t="n">
+        <v>989</v>
+      </c>
+      <c r="B990" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.pillarNumber</t>
+        </is>
+      </c>
+      <c r="D990" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E990" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F990" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H990" s="22" t="inlineStr">
+        <is>
+          <t>[Index number]</t>
+        </is>
+      </c>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="15" t="n"/>
-      <c r="B991" s="16" t="n"/>
+      <c r="A991" s="15" t="n">
+        <v>990</v>
+      </c>
+      <c r="B991" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item1Title</t>
+        </is>
+      </c>
+      <c r="D991" s="22" t="inlineStr">
+        <is>
+          <t>Saúde e Expressão</t>
+        </is>
+      </c>
+      <c r="E991" s="22" t="inlineStr">
+        <is>
+          <t>Health &amp; Expression</t>
+        </is>
+      </c>
+      <c r="F991" s="22" t="inlineStr">
+        <is>
+          <t>Helse og Utfoldelse</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H991" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'Utfoldelse' captures artistic and physical expression]</t>
+        </is>
+      </c>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="15" t="n"/>
-      <c r="B992" s="16" t="n"/>
+      <c r="A992" s="15" t="n">
+        <v>991</v>
+      </c>
+      <c r="B992" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item1Desc</t>
+        </is>
+      </c>
+      <c r="D992" s="22" t="inlineStr">
+        <is>
+          <t>Investimento direto em bem-estar físico e mental, criatividade e desenvolvimento artístico com orientação profissional de excelência.</t>
+        </is>
+      </c>
+      <c r="E992" s="22" t="inlineStr">
+        <is>
+          <t>A direct investment in physical and mental wellbeing, creativity, and artistic growth under exceptional professional guidance.</t>
+        </is>
+      </c>
+      <c r="F992" s="22" t="inlineStr">
+        <is>
+          <t>En direkte investering i fysisk og mental helse, kreativitet og kunstnerisk vekst under profesjonell veiledning på høyt nivå.</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H992" s="22" t="inlineStr">
+        <is>
+          <t>[Holistic somatic/artistic benefits]</t>
+        </is>
+      </c>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="15" t="n"/>
-      <c r="B993" s="16" t="n"/>
+      <c r="A993" s="15" t="n">
+        <v>992</v>
+      </c>
+      <c r="B993" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item2Title</t>
+        </is>
+      </c>
+      <c r="D993" s="22" t="inlineStr">
+        <is>
+          <t>Conexões Reais &amp; Presença</t>
+        </is>
+      </c>
+      <c r="E993" s="22" t="inlineStr">
+        <is>
+          <t>Authentic Connections &amp; Presence</t>
+        </is>
+      </c>
+      <c r="F993" s="22" t="inlineStr">
+        <is>
+          <t>Ekte Menneskemøter &amp; Nærvær</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H993" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'Menneskemøter' is a deep Norwegian cultural concept]</t>
+        </is>
+      </c>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="15" t="n"/>
-      <c r="B994" s="16" t="n"/>
+      <c r="A994" s="15" t="n">
+        <v>993</v>
+      </c>
+      <c r="B994" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item2Desc</t>
+        </is>
+      </c>
+      <c r="D994" s="22" t="inlineStr">
+        <is>
+          <t>Encontros humanos autênticos em um espaço seguro e acolhedor, onde o movimento expande a percepção e a vitalidade criativa.</t>
+        </is>
+      </c>
+      <c r="E994" s="22" t="inlineStr">
+        <is>
+          <t>Genuine human encounters in a safe and welcoming space, where movement expands awareness and creative vitality.</t>
+        </is>
+      </c>
+      <c r="F994" s="22" t="inlineStr">
+        <is>
+          <t>Ekte menneskemøter i et trygt og inkluderende rom, der bevegelse åpner for dypere oppmerksomhet og skaperglede.</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H994" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'skaperglede' evokes artistic joy and vitality naturally]</t>
+        </is>
+      </c>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="15" t="n"/>
-      <c r="B995" s="16" t="n"/>
+      <c r="A995" s="15" t="n">
+        <v>994</v>
+      </c>
+      <c r="B995" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item3Title</t>
+        </is>
+      </c>
+      <c r="D995" s="22" t="inlineStr">
+        <is>
+          <t>Impacto Social Compartilhado</t>
+        </is>
+      </c>
+      <c r="E995" s="22" t="inlineStr">
+        <is>
+          <t>Shared Social Impact</t>
+        </is>
+      </c>
+      <c r="F995" s="22" t="inlineStr">
+        <is>
+          <t>Felles Samfunnsansvar</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H995" s="22" t="inlineStr">
+        <is>
+          <t>[Ethical solidarity concept]</t>
+        </is>
+      </c>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="15" t="n"/>
-      <c r="B996" s="16" t="n"/>
+      <c r="A996" s="15" t="n">
+        <v>995</v>
+      </c>
+      <c r="B996" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>pricingPage.payerCard.item3Desc</t>
+        </is>
+      </c>
+      <c r="D996" s="22" t="inlineStr">
+        <is>
+          <t>Para quem tem condições financeiras, a taxa de inscrição reflete um valor justo de mercado. Esse valor cobre custos de produção e co-financia diretamente as bolsas comunitárias.</t>
+        </is>
+      </c>
+      <c r="E996" s="22" t="inlineStr">
+        <is>
+          <t>For those with the financial means, our fees reflect fair market rates. This investment covers production costs and directly co-funds full scholarships for our local community.</t>
+        </is>
+      </c>
+      <c r="F996" s="22" t="inlineStr">
+        <is>
+          <t>For dem med betalingsevne reflekterer kursavgiften en rettferdig markedspris. Dette dekker produksjonskostnader og er med på å finansiere fulle stipendplasser for lokalmiljøet.</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H996" s="22" t="inlineStr">
+        <is>
+          <t>[Clear explanation of fee redistribution]</t>
+        </is>
+      </c>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="15" t="n"/>
-      <c r="B997" s="16" t="n"/>
+      <c r="A997" s="15" t="n">
+        <v>996</v>
+      </c>
+      <c r="B997" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.kicker</t>
+        </is>
+      </c>
+      <c r="D997" s="22" t="inlineStr">
+        <is>
+          <t>Impacto Local &amp; Equidade</t>
+        </is>
+      </c>
+      <c r="E997" s="22" t="inlineStr">
+        <is>
+          <t>Local Impact &amp; Equity</t>
+        </is>
+      </c>
+      <c r="F997" s="22" t="inlineStr">
+        <is>
+          <t>Lokal Inkludering &amp; Likeverd</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H997" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'Likeverd' reflects Norwegian egalitarian values]</t>
+        </is>
+      </c>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="15" t="n"/>
-      <c r="B998" s="16" t="n"/>
+      <c r="A998" s="15" t="n">
+        <v>997</v>
+      </c>
+      <c r="B998" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.title</t>
+        </is>
+      </c>
+      <c r="D998" s="22" t="inlineStr">
+        <is>
+          <t>Bolsas Integrais de 100%</t>
+        </is>
+      </c>
+      <c r="E998" s="22" t="inlineStr">
+        <is>
+          <t>100% Full Scholarships</t>
+        </is>
+      </c>
+      <c r="F998" s="22" t="inlineStr">
+        <is>
+          <t>100 % Fulle Stipend</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H998" s="22" t="inlineStr">
+        <is>
+          <t>[Norwegian typography uses space before percentage sign]</t>
+        </is>
+      </c>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="15" t="n"/>
-      <c r="B999" s="16" t="n"/>
+      <c r="A999" s="15" t="n">
+        <v>998</v>
+      </c>
+      <c r="B999" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.subtitle</t>
+        </is>
+      </c>
+      <c r="D999" s="22" t="inlineStr">
+        <is>
+          <t>Para quem participa por bolsa</t>
+        </is>
+      </c>
+      <c r="E999" s="22" t="inlineStr">
+        <is>
+          <t>For scholarship participants</t>
+        </is>
+      </c>
+      <c r="F999" s="22" t="inlineStr">
+        <is>
+          <t>For deg på stipend</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H999" s="22" t="inlineStr">
+        <is>
+          <t>[Symmetrical second-person address matching 'For deg som investerer']</t>
+        </is>
+      </c>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="15" t="n"/>
-      <c r="B1000" s="16" t="n"/>
+      <c r="A1000" s="15" t="n">
+        <v>999</v>
+      </c>
+      <c r="B1000" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.pillarNumber</t>
+        </is>
+      </c>
+      <c r="D1000" s="22" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E1000" s="22" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F1000" s="22" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1000" s="22" t="inlineStr">
+        <is>
+          <t>[Index number]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B1001" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item1Title</t>
+        </is>
+      </c>
+      <c r="D1001" s="22" t="inlineStr">
+        <is>
+          <t>Gratuidade Total</t>
+        </is>
+      </c>
+      <c r="E1001" s="22" t="inlineStr">
+        <is>
+          <t>Zero Cost</t>
+        </is>
+      </c>
+      <c r="F1001" s="22" t="inlineStr">
+        <is>
+          <t>Helt Kostnadsfritt</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1001" s="22" t="inlineStr">
+        <is>
+          <t>[Dignified term over colloquial 'gratis']</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="15" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B1002" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item1Desc</t>
+        </is>
+      </c>
+      <c r="D1002" s="22" t="inlineStr">
+        <is>
+          <t>Moradores de Tøyen e Grønland têm a possibilidade de acesso gratuito a qualquer uma de nossas atividades por meio de bolsas integrais.</t>
+        </is>
+      </c>
+      <c r="E1002" s="22" t="inlineStr">
+        <is>
+          <t>Residents of Tøyen and Grønland have the opportunity to access any of our activities completely free through full scholarships.</t>
+        </is>
+      </c>
+      <c r="F1002" s="22" t="inlineStr">
+        <is>
+          <t>Beboere på Tøyen og Grønland har mulighet til fri deltakelse på alle våre aktiviteter gjennom fulle stipend.</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1002" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'fri deltakelse' is elegant and dignified]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="15" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B1003" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item2Title</t>
+        </is>
+      </c>
+      <c r="D1003" s="22" t="inlineStr">
+        <is>
+          <t>Vocação e Novos Potenciais</t>
+        </is>
+      </c>
+      <c r="E1003" s="22" t="inlineStr">
+        <is>
+          <t>Calling &amp; New Potential</t>
+        </is>
+      </c>
+      <c r="F1003" s="22" t="inlineStr">
+        <is>
+          <t>Yrkesvei &amp; Nye Muligheter</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1003" s="22" t="inlineStr">
+        <is>
+          <t>[Professional and creative development]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="15" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B1004" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item2Desc</t>
+        </is>
+      </c>
+      <c r="D1004" s="22" t="inlineStr">
+        <is>
+          <t>Uma oportunidade de descobrir a própria vocação profissional, desbloquear potenciais criativos e abrir caminhos para o autodesenvolvimento.</t>
+        </is>
+      </c>
+      <c r="E1004" s="22" t="inlineStr">
+        <is>
+          <t>An opportunity to discover your professional calling, unlock creative potential, and open meaningful paths for personal and artistic growth.</t>
+        </is>
+      </c>
+      <c r="F1004" s="22" t="inlineStr">
+        <is>
+          <t>En mulighet til å oppdage egen yrkesretning, frigjøre kreativt potensial og åpne nye dører for personlig utvikling.</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1004" s="22" t="inlineStr">
+        <is>
+          <t>[Empowering growth narrative]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="15" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B1005" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item3Title</t>
+        </is>
+      </c>
+      <c r="D1005" s="22" t="inlineStr">
+        <is>
+          <t>A Mesma Excelência</t>
+        </is>
+      </c>
+      <c r="E1005" s="22" t="inlineStr">
+        <is>
+          <t>Equal Excellence</t>
+        </is>
+      </c>
+      <c r="F1005" s="22" t="inlineStr">
+        <is>
+          <t>Samme Høye Kvalitet</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1005" s="22" t="inlineStr">
+        <is>
+          <t>[Reassurance of equal quality]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="15" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B1006" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>pricingPage.communityCard.item3Desc</t>
+        </is>
+      </c>
+      <c r="D1006" s="22" t="inlineStr">
+        <is>
+          <t>O mesmo estúdio, os mesmos instrutores e o mesmo rigor técnico. Uma porta aberta para a cultura no coração do seu próprio bairro, sem distinções ou concessões.</t>
+        </is>
+      </c>
+      <c r="E1006" s="22" t="inlineStr">
+        <is>
+          <t>The same studio, the same teachers, and the same artistic rigor. An open door to culture in the heart of your neighborhood, without distinctions or compromise.</t>
+        </is>
+      </c>
+      <c r="F1006" s="22" t="inlineStr">
+        <is>
+          <t>Samme dansesal, samme instruktører og samme faglige grundighet. En åpen dør til kultur i hjertet av ditt eget nabolag, uten kompromisser eller forskjellsbehandling.</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1006" s="22" t="inlineStr">
+        <is>
+          <t>[NO: 'forskjellsbehandling' is the exact Norwegian concept for unfair distinctions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="15" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B1007" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>pricingPage.manifesto.title</t>
+        </is>
+      </c>
+      <c r="D1007" s="22" t="inlineStr">
+        <is>
+          <t>Transparência absoluta.</t>
+        </is>
+      </c>
+      <c r="E1007" s="22" t="inlineStr">
+        <is>
+          <t>Absolute transparency.</t>
+        </is>
+      </c>
+      <c r="F1007" s="22" t="inlineStr">
+        <is>
+          <t>Full åpenhet.</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1007" s="22" t="inlineStr">
+        <is>
+          <t>[Clear, concise manifesto header]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="15" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B1008" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>pricingPage.manifesto.body</t>
+        </is>
+      </c>
+      <c r="D1008" s="22" t="inlineStr">
+        <is>
+          <t>Quem investe financeiramente sabe com clareza o valor do que recebe e o impacto social do seu recurso. E quem ingressa por bolsa integral tem assegurado um ambiente de respeito mútuo e dignidade.</t>
+        </is>
+      </c>
+      <c r="E1008" s="22" t="inlineStr">
+        <is>
+          <t>Those who invest financially clearly see the value of what they receive and the social impact of their contribution. Those who join through full scholarships are assured an environment of mutual respect and dignity.</t>
+        </is>
+      </c>
+      <c r="F1008" s="22" t="inlineStr">
+        <is>
+          <t>De som investerer økonomisk, ser tydelig verdien av det de mottar og samfunnseffekten av sitt bidrag. De som deltar på fullt stipend, møter et miljø preget av gjensidig respekt og verdighet.</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1008" s="22" t="inlineStr">
+        <is>
+          <t>[Philosophical alignment of paying and scholarship participants]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="15" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B1009" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>pricingPage.manifesto.subtext</t>
+        </is>
+      </c>
+      <c r="D1009" s="22" t="inlineStr">
+        <is>
+          <t>A receita de workshops é apenas o primeiro dos quatro pilares de sustentabilidade do Dance2Dance.</t>
+        </is>
+      </c>
+      <c r="E1009" s="22" t="inlineStr">
+        <is>
+          <t>Workshop revenue is only the first of four sustainability pillars at Dance2Dance.</t>
+        </is>
+      </c>
+      <c r="F1009" s="22" t="inlineStr">
+        <is>
+          <t>Inntekter fra workshops er bare den første av fire bærekraftspilarer i Dance2Dance.</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1009" s="22" t="inlineStr">
+        <is>
+          <t>[Reference to broader NGO financing model]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="15" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B1010" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>pricingPage.manifesto.linkText</t>
+        </is>
+      </c>
+      <c r="D1010" s="22" t="inlineStr">
+        <is>
+          <t>Conheça nosso ecossistema financeiro completo no Projeto Social</t>
+        </is>
+      </c>
+      <c r="E1010" s="22" t="inlineStr">
+        <is>
+          <t>Explore our full financial model on the Social Project page</t>
+        </is>
+      </c>
+      <c r="F1010" s="22" t="inlineStr">
+        <is>
+          <t>Les om hele vår økonomiske modell på siden for samfunnsprosjektet</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1010" s="22" t="inlineStr">
+        <is>
+          <t>[Link text pointing to social project]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B1011" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.kicker</t>
+        </is>
+      </c>
+      <c r="D1011" s="22" t="inlineStr">
+        <is>
+          <t>Transparência Objetiva</t>
+        </is>
+      </c>
+      <c r="E1011" s="22" t="inlineStr">
+        <is>
+          <t>Clear &amp; Transparent</t>
+        </is>
+      </c>
+      <c r="F1011" s="22" t="inlineStr">
+        <is>
+          <t>Klar Oversikt</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1011" s="22" t="inlineStr">
+        <is>
+          <t>[Section kicker]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B1012" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.title</t>
+        </is>
+      </c>
+      <c r="D1012" s="22" t="inlineStr">
+        <is>
+          <t>Workshops &amp; Formações</t>
+        </is>
+      </c>
+      <c r="E1012" s="22" t="inlineStr">
+        <is>
+          <t>Workshops &amp; Courses</t>
+        </is>
+      </c>
+      <c r="F1012" s="22" t="inlineStr">
+        <is>
+          <t>Workshops &amp; Kurs</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1012" s="22" t="inlineStr">
+        <is>
+          <t>[Section title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="15" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B1013" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.allFilter</t>
+        </is>
+      </c>
+      <c r="D1013" s="22" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E1013" s="22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F1013" s="22" t="inlineStr">
+        <is>
+          <t>Alle</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1013" s="22" t="inlineStr">
+        <is>
+          <t>[Filter tab: all programs]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="15" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B1014" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.hoursUnit</t>
+        </is>
+      </c>
+      <c r="D1014" s="22" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E1014" s="22" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="F1014" s="22" t="inlineStr">
+        <is>
+          <t>timer</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1014" s="22" t="inlineStr">
+        <is>
+          <t>[Time unit]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="15" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B1015" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.spotsInfo</t>
+        </is>
+      </c>
+      <c r="D1015" s="22" t="inlineStr">
+        <is>
+          <t>Vagas limitadas por turma</t>
+        </is>
+      </c>
+      <c r="E1015" s="22" t="inlineStr">
+        <is>
+          <t>Limited spots per group</t>
+        </is>
+      </c>
+      <c r="F1015" s="22" t="inlineStr">
+        <is>
+          <t>Begrenset antall plasser</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1015" s="22" t="inlineStr">
+        <is>
+          <t>[Spots disclaimer]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="15" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B1016" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>pricingPage.rates.learnMore</t>
+        </is>
+      </c>
+      <c r="D1016" s="22" t="inlineStr">
+        <is>
+          <t>Saiba mais</t>
+        </is>
+      </c>
+      <c r="E1016" s="22" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="F1016" s="22" t="inlineStr">
+        <is>
+          <t>Les mer</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1016" s="22" t="inlineStr">
+        <is>
+          <t>[CTA button]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="15" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B1017" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.kicker</t>
+        </is>
+      </c>
+      <c r="D1017" s="22" t="inlineStr">
+        <is>
+          <t>Parcerias &amp; Organizações</t>
+        </is>
+      </c>
+      <c r="E1017" s="22" t="inlineStr">
+        <is>
+          <t>Partnerships &amp; Organizations</t>
+        </is>
+      </c>
+      <c r="F1017" s="22" t="inlineStr">
+        <is>
+          <t>Bedrifter &amp; Samarbeid</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1017" s="22" t="inlineStr">
+        <is>
+          <t>[Corporate kicker]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="15" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B1018" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.title</t>
+        </is>
+      </c>
+      <c r="D1018" s="22" t="inlineStr">
+        <is>
+          <t>Formato para Empresas</t>
+        </is>
+      </c>
+      <c r="E1018" s="22" t="inlineStr">
+        <is>
+          <t>Corporate Formats</t>
+        </is>
+      </c>
+      <c r="F1018" s="22" t="inlineStr">
+        <is>
+          <t>Formater for Bedrifter</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1018" s="22" t="inlineStr">
+        <is>
+          <t>[Corporate section title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="15" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B1019" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.subtitle</t>
+        </is>
+      </c>
+      <c r="D1019" s="22" t="inlineStr">
+        <is>
+          <t>Programas customizados para empresas e equipes.</t>
+        </is>
+      </c>
+      <c r="E1019" s="22" t="inlineStr">
+        <is>
+          <t>Tailored programs for organizations and teams.</t>
+        </is>
+      </c>
+      <c r="F1019" s="22" t="inlineStr">
+        <is>
+          <t>Skreddersydde programmer for bedrifter og team.</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1019" s="22" t="inlineStr">
+        <is>
+          <t>[Corporate subtitle]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="15" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B1020" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.btdTitle</t>
+        </is>
+      </c>
+      <c r="D1020" s="22" t="inlineStr">
+        <is>
+          <t>Be the Dance in Company</t>
+        </is>
+      </c>
+      <c r="E1020" s="22" t="inlineStr">
+        <is>
+          <t>Be the Dance in Company</t>
+        </is>
+      </c>
+      <c r="F1020" s="22" t="inlineStr">
+        <is>
+          <t>Be the Dance in Company</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1020" s="22" t="inlineStr">
+        <is>
+          <t>[Program title with standardized casing]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B1021" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.btdDesc</t>
+        </is>
+      </c>
+      <c r="D1021" s="22" t="inlineStr">
+        <is>
+          <t>Dinâmicas integrativas de presença, ritmo e expressão corporal para equipes corporativas.</t>
+        </is>
+      </c>
+      <c r="E1021" s="22" t="inlineStr">
+        <is>
+          <t>Integrative sessions focused on presence, rhythm, and embodied expression for workplace teams.</t>
+        </is>
+      </c>
+      <c r="F1021" s="22" t="inlineStr">
+        <is>
+          <t>Teambygging og tilstedeværelse med fokus på rytme, kroppsbevissthet og fellesskap.</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1021" s="22" t="inlineStr">
+        <is>
+          <t>[BTD corporate description]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="15" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B1022" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.bioTitle</t>
+        </is>
+      </c>
+      <c r="D1022" s="22" t="inlineStr">
+        <is>
+          <t>Biostretch in Company</t>
+        </is>
+      </c>
+      <c r="E1022" s="22" t="inlineStr">
+        <is>
+          <t>Biostretch in Company</t>
+        </is>
+      </c>
+      <c r="F1022" s="22" t="inlineStr">
+        <is>
+          <t>Biostretch in Company</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1022" s="22" t="inlineStr">
+        <is>
+          <t>[Program title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="15" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B1023" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.bioDesc</t>
+        </is>
+      </c>
+      <c r="D1023" s="22" t="inlineStr">
+        <is>
+          <t>Ergonomia postural, alívio de tensões e descompressão do estresse no ambiente de trabalho.</t>
+        </is>
+      </c>
+      <c r="E1023" s="22" t="inlineStr">
+        <is>
+          <t>Postural ergonomics, tension release, and stress relief tailored for the workplace.</t>
+        </is>
+      </c>
+      <c r="F1023" s="22" t="inlineStr">
+        <is>
+          <t>Holdningskorrigering, avspenning og stressmestring tilpasset arbeidsplassen.</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1023" s="22" t="inlineStr">
+        <is>
+          <t>[Biostretch corporate description]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="15" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B1024" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>pricingPage.corporateSection.learnMore</t>
+        </is>
+      </c>
+      <c r="D1024" s="22" t="inlineStr">
+        <is>
+          <t>Saiba mais</t>
+        </is>
+      </c>
+      <c r="E1024" s="22" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
+      <c r="F1024" s="22" t="inlineStr">
+        <is>
+          <t>Les mer</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1024" s="22" t="inlineStr">
+        <is>
+          <t>[CTA button]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="15" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B1025" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>pricingPage.finalCta.titleLead</t>
+        </is>
+      </c>
+      <c r="D1025" s="22" t="inlineStr">
+        <is>
+          <t>oferece cursos originais e exclusivos.</t>
+        </is>
+      </c>
+      <c r="E1025" s="22" t="inlineStr">
+        <is>
+          <t>offers original and immersive courses.</t>
+        </is>
+      </c>
+      <c r="F1025" s="22" t="inlineStr">
+        <is>
+          <t>tilbyr originale og eksklusive kurs.</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1025" s="22" t="inlineStr">
+        <is>
+          <t>[Sentence continuing after Dance2Dance logo]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="15" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B1026" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>pricingPage.finalCta.subtitle</t>
+        </is>
+      </c>
+      <c r="D1026" s="22" t="inlineStr">
+        <is>
+          <t>Descubra a programação completa dos nossos próximos encontros e garanta o seu lugar.</t>
+        </is>
+      </c>
+      <c r="E1026" s="22" t="inlineStr">
+        <is>
+          <t>Discover the full schedule of our upcoming sessions and reserve your place.</t>
+        </is>
+      </c>
+      <c r="F1026" s="22" t="inlineStr">
+        <is>
+          <t>Utforsk timeplanen for våre kommende kurs og sikre din plass.</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1026" s="22" t="inlineStr">
+        <is>
+          <t>[CTA subtitle]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="15" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B1027" s="16" t="inlineStr">
+        <is>
+          <t>pricingPage</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>pricingPage.finalCta.btn</t>
+        </is>
+      </c>
+      <c r="D1027" s="22" t="inlineStr">
+        <is>
+          <t>Ver agenda completa</t>
+        </is>
+      </c>
+      <c r="E1027" s="22" t="inlineStr">
+        <is>
+          <t>View full schedule</t>
+        </is>
+      </c>
+      <c r="F1027" s="22" t="inlineStr">
+        <is>
+          <t>Se hele timeplanen</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1027" s="22" t="inlineStr">
+        <is>
+          <t>[Button linking to agenda]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="15" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B1028" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>adminPage.masterTabWishlist</t>
+        </is>
+      </c>
+      <c r="D1028" s="22" t="inlineStr">
+        <is>
+          <t>Demandas &amp; Wishlist</t>
+        </is>
+      </c>
+      <c r="E1028" s="22" t="inlineStr">
+        <is>
+          <t>Demand &amp; Wishlist</t>
+        </is>
+      </c>
+      <c r="F1028" s="22" t="inlineStr">
+        <is>
+          <t>Etterspørsel &amp; Ønskeliste</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1028" s="22" t="inlineStr">
+        <is>
+          <t>[Admin navigation tab]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="15" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B1029" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>adminPage.ready</t>
+        </is>
+      </c>
+      <c r="D1029" s="22" t="inlineStr">
+        <is>
+          <t>Pronto para Agendar</t>
+        </is>
+      </c>
+      <c r="E1029" s="22" t="inlineStr">
+        <is>
+          <t>Ready to Schedule</t>
+        </is>
+      </c>
+      <c r="F1029" s="22" t="inlineStr">
+        <is>
+          <t>Klar til Oppsetting</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1029" s="22" t="inlineStr">
+        <is>
+          <t>[Cohort readiness indicator]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="15" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B1030" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.alertReadyDesc</t>
+        </is>
+      </c>
+      <c r="D1030" s="22" t="inlineStr">
+        <is>
+          <t>Há demanda confirmada para a abertura de novas turmas na agenda.</t>
+        </is>
+      </c>
+      <c r="E1030" s="22" t="inlineStr">
+        <is>
+          <t>There is confirmed demand to schedule new workshop cohorts.</t>
+        </is>
+      </c>
+      <c r="F1030" s="22" t="inlineStr">
+        <is>
+          <t>Det er bekreftet etterspørsel for oppstart av nye workshop-grupper.</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1030" s="22" t="inlineStr">
+        <is>
+          <t>[Admin banner alert]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="15" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B1031" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.viewReadyOnly</t>
+        </is>
+      </c>
+      <c r="D1031" s="22" t="inlineStr">
+        <is>
+          <t>Ver Prontos para Agendar</t>
+        </is>
+      </c>
+      <c r="E1031" s="22" t="inlineStr">
+        <is>
+          <t>View Ready to Schedule</t>
+        </is>
+      </c>
+      <c r="F1031" s="22" t="inlineStr">
+        <is>
+          <t>Se Klare til Oppsetting</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1031" s="22" t="inlineStr">
+        <is>
+          <t>[Admin button filter]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="15" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B1032" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.totalWishes</t>
+        </is>
+      </c>
+      <c r="D1032" s="22" t="inlineStr">
+        <is>
+          <t>Desejos Registrados</t>
+        </is>
+      </c>
+      <c r="E1032" s="22" t="inlineStr">
+        <is>
+          <t>Registered Wishes</t>
+        </is>
+      </c>
+      <c r="F1032" s="22" t="inlineStr">
+        <is>
+          <t>Registrerte Ønsker</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1032" s="22" t="inlineStr">
+        <is>
+          <t>[Metric card title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="15" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B1033" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.workshopsWithDemand</t>
+        </is>
+      </c>
+      <c r="D1033" s="22" t="inlineStr">
+        <is>
+          <t>Workshops com Demanda</t>
+        </is>
+      </c>
+      <c r="E1033" s="22" t="inlineStr">
+        <is>
+          <t>Workshops with Demand</t>
+        </is>
+      </c>
+      <c r="F1033" s="22" t="inlineStr">
+        <is>
+          <t>Workshoper med Etterspørsel</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1033" s="22" t="inlineStr">
+        <is>
+          <t>[Metric card title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="15" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B1034" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.goalsReached</t>
+        </is>
+      </c>
+      <c r="D1034" s="22" t="inlineStr">
+        <is>
+          <t>Metas Atingidas (10+)</t>
+        </is>
+      </c>
+      <c r="E1034" s="22" t="inlineStr">
+        <is>
+          <t>Goals Reached (10+)</t>
+        </is>
+      </c>
+      <c r="F1034" s="22" t="inlineStr">
+        <is>
+          <t>Nådde Mål (10+)</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1034" s="22" t="inlineStr">
+        <is>
+          <t>[Metric card title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="15" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B1035" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.inProgress</t>
+        </is>
+      </c>
+      <c r="D1035" s="22" t="inlineStr">
+        <is>
+          <t>Em Captação (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="E1035" s="22" t="inlineStr">
+        <is>
+          <t>In Progress (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="F1035" s="22" t="inlineStr">
+        <is>
+          <t>Under Innsamling (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1035" s="22" t="inlineStr">
+        <is>
+          <t>[Metric card title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="15" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B1036" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.searchPlaceholder</t>
+        </is>
+      </c>
+      <c r="D1036" s="22" t="inlineStr">
+        <is>
+          <t>Buscar por workshop ou nome/email de aluno...</t>
+        </is>
+      </c>
+      <c r="E1036" s="22" t="inlineStr">
+        <is>
+          <t>Search by workshop or student name/email...</t>
+        </is>
+      </c>
+      <c r="F1036" s="22" t="inlineStr">
+        <is>
+          <t>Søk etter workshop eller elevens navn/e-post...</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1036" s="22" t="inlineStr">
+        <is>
+          <t>[Search input placeholder]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="15" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B1037" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.filterAllStatus</t>
+        </is>
+      </c>
+      <c r="D1037" s="22" t="inlineStr">
+        <is>
+          <t>Todos os Status</t>
+        </is>
+      </c>
+      <c r="E1037" s="22" t="inlineStr">
+        <is>
+          <t>All Statuses</t>
+        </is>
+      </c>
+      <c r="F1037" s="22" t="inlineStr">
+        <is>
+          <t>Alle Statuser</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1037" s="22" t="inlineStr">
+        <is>
+          <t>[Filter option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="15" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B1038" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.filterGoalReached</t>
+        </is>
+      </c>
+      <c r="D1038" s="22" t="inlineStr">
+        <is>
+          <t>Metas Atingidas (10+)</t>
+        </is>
+      </c>
+      <c r="E1038" s="22" t="inlineStr">
+        <is>
+          <t>Goals Reached (10+)</t>
+        </is>
+      </c>
+      <c r="F1038" s="22" t="inlineStr">
+        <is>
+          <t>Nådde Mål (10+)</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1038" s="22" t="inlineStr">
+        <is>
+          <t>[Filter option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="15" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B1039" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.filterInProgress</t>
+        </is>
+      </c>
+      <c r="D1039" s="22" t="inlineStr">
+        <is>
+          <t>Em Andamento (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="E1039" s="22" t="inlineStr">
+        <is>
+          <t>In Progress (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="F1039" s="22" t="inlineStr">
+        <is>
+          <t>Underveis (&lt; 10)</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1039" s="22" t="inlineStr">
+        <is>
+          <t>[Filter option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="15" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B1040" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.filterAllCategories</t>
+        </is>
+      </c>
+      <c r="D1040" s="22" t="inlineStr">
+        <is>
+          <t>Todas Categorias</t>
+        </is>
+      </c>
+      <c r="E1040" s="22" t="inlineStr">
+        <is>
+          <t>All Categories</t>
+        </is>
+      </c>
+      <c r="F1040" s="22" t="inlineStr">
+        <is>
+          <t>Alle Kategorier</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1040" s="22" t="inlineStr">
+        <is>
+          <t>[Filter option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="15" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1041" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.sortMostWished</t>
+        </is>
+      </c>
+      <c r="D1041" s="22" t="inlineStr">
+        <is>
+          <t>Mais Interessados</t>
+        </is>
+      </c>
+      <c r="E1041" s="22" t="inlineStr">
+        <is>
+          <t>Most Interested</t>
+        </is>
+      </c>
+      <c r="F1041" s="22" t="inlineStr">
+        <is>
+          <t>Mest Populære</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1041" s="22" t="inlineStr">
+        <is>
+          <t>[Sort option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="15" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B1042" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.sortRecent</t>
+        </is>
+      </c>
+      <c r="D1042" s="22" t="inlineStr">
+        <is>
+          <t>Mais Recentes</t>
+        </is>
+      </c>
+      <c r="E1042" s="22" t="inlineStr">
+        <is>
+          <t>Most Recent</t>
+        </is>
+      </c>
+      <c r="F1042" s="22" t="inlineStr">
+        <is>
+          <t>Nyeste</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1042" s="22" t="inlineStr">
+        <is>
+          <t>[Sort option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="15" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B1043" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.sortName</t>
+        </is>
+      </c>
+      <c r="D1043" s="22" t="inlineStr">
+        <is>
+          <t>Nome do Workshop</t>
+        </is>
+      </c>
+      <c r="E1043" s="22" t="inlineStr">
+        <is>
+          <t>Workshop Name</t>
+        </is>
+      </c>
+      <c r="F1043" s="22" t="inlineStr">
+        <is>
+          <t>Workshop-navn</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1043" s="22" t="inlineStr">
+        <is>
+          <t>[Sort option]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="15" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B1044" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.noResultsTitle</t>
+        </is>
+      </c>
+      <c r="D1044" s="22" t="inlineStr">
+        <is>
+          <t>Nenhuma demanda encontrada</t>
+        </is>
+      </c>
+      <c r="E1044" s="22" t="inlineStr">
+        <is>
+          <t>No demands found</t>
+        </is>
+      </c>
+      <c r="F1044" s="22" t="inlineStr">
+        <is>
+          <t>Ingen etterspørsler funnet</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1044" s="22" t="inlineStr">
+        <is>
+          <t>[Empty state title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="15" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B1045" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.noResultsFilter</t>
+        </is>
+      </c>
+      <c r="D1045" s="22" t="inlineStr">
+        <is>
+          <t>Tente ajustar os filtros ou a busca acima.</t>
+        </is>
+      </c>
+      <c r="E1045" s="22" t="inlineStr">
+        <is>
+          <t>Try adjusting the filters or search above.</t>
+        </is>
+      </c>
+      <c r="F1045" s="22" t="inlineStr">
+        <is>
+          <t>Prøv å justere filtrene eller søket ovenfor.</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1045" s="22" t="inlineStr">
+        <is>
+          <t>[Empty state hint]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="15" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B1046" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.noWishesYet</t>
+        </is>
+      </c>
+      <c r="D1046" s="22" t="inlineStr">
+        <is>
+          <t>Assim que os alunos demonstrarem interesse pelos workshops sem data definida, os pedidos aparecerão aqui.</t>
+        </is>
+      </c>
+      <c r="E1046" s="22" t="inlineStr">
+        <is>
+          <t>As soon as students express interest in unscheduled workshops, their wishes will appear here.</t>
+        </is>
+      </c>
+      <c r="F1046" s="22" t="inlineStr">
+        <is>
+          <t>Så snart elever melder interesse for workshoper uten oppsatt dato, vil ønskene vises her.</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1046" s="22" t="inlineStr">
+        <is>
+          <t>[Empty state description]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="15" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B1047" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.goalReachedTag</t>
+        </is>
+      </c>
+      <c r="D1047" s="22" t="inlineStr">
+        <is>
+          <t>Meta Atingida!</t>
+        </is>
+      </c>
+      <c r="E1047" s="22" t="inlineStr">
+        <is>
+          <t>Goal Reached!</t>
+        </is>
+      </c>
+      <c r="F1047" s="22" t="inlineStr">
+        <is>
+          <t>Målet er Nådd!</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1047" s="22" t="inlineStr">
+        <is>
+          <t>[Badge tag]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="15" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1048" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.interested</t>
+        </is>
+      </c>
+      <c r="D1048" s="22" t="inlineStr">
+        <is>
+          <t>interessados</t>
+        </is>
+      </c>
+      <c r="E1048" s="22" t="inlineStr">
+        <is>
+          <t>interested</t>
+        </is>
+      </c>
+      <c r="F1048" s="22" t="inlineStr">
+        <is>
+          <t>interesserte</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1048" s="22" t="inlineStr">
+        <is>
+          <t>[Count suffix]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="15" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1049" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.viewWorkshopPage</t>
+        </is>
+      </c>
+      <c r="D1049" s="22" t="inlineStr">
+        <is>
+          <t>Ver página do workshop</t>
+        </is>
+      </c>
+      <c r="E1049" s="22" t="inlineStr">
+        <is>
+          <t>View workshop page</t>
+        </is>
+      </c>
+      <c r="F1049" s="22" t="inlineStr">
+        <is>
+          <t>Vis workshop-side</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1049" s="22" t="inlineStr">
+        <is>
+          <t>[Action link]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="15" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1050" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.progressToGoal</t>
+        </is>
+      </c>
+      <c r="D1050" s="22" t="inlineStr">
+        <is>
+          <t>Progresso para abertura de turma</t>
+        </is>
+      </c>
+      <c r="E1050" s="22" t="inlineStr">
+        <is>
+          <t>Progress toward cohort opening</t>
+        </is>
+      </c>
+      <c r="F1050" s="22" t="inlineStr">
+        <is>
+          <t>Fremgang mot gruppeoppstart</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1050" s="22" t="inlineStr">
+        <is>
+          <t>[Progress bar title]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="15" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1051" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.scheduleTooltip</t>
+        </is>
+      </c>
+      <c r="D1051" s="22" t="inlineStr">
+        <is>
+          <t>Abrir formulário e agendar este workshop</t>
+        </is>
+      </c>
+      <c r="E1051" s="22" t="inlineStr">
+        <is>
+          <t>Open form and schedule this workshop</t>
+        </is>
+      </c>
+      <c r="F1051" s="22" t="inlineStr">
+        <is>
+          <t>Åpne skjema og sett opp denne workshopen</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1051" s="22" t="inlineStr">
+        <is>
+          <t>[Button tooltip]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="15" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1052" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.scheduleBtn</t>
+        </is>
+      </c>
+      <c r="D1052" s="22" t="inlineStr">
+        <is>
+          <t>Agendar Workshop</t>
+        </is>
+      </c>
+      <c r="E1052" s="22" t="inlineStr">
+        <is>
+          <t>Schedule Workshop</t>
+        </is>
+      </c>
+      <c r="F1052" s="22" t="inlineStr">
+        <is>
+          <t>Sett opp Workshop</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1052" s="22" t="inlineStr">
+        <is>
+          <t>[Action button]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="15" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1053" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.copyEmailsTooltip</t>
+        </is>
+      </c>
+      <c r="D1053" s="22" t="inlineStr">
+        <is>
+          <t>Copiar e-mails de todos os interessados</t>
+        </is>
+      </c>
+      <c r="E1053" s="22" t="inlineStr">
+        <is>
+          <t>Copy emails of all interested students</t>
+        </is>
+      </c>
+      <c r="F1053" s="22" t="inlineStr">
+        <is>
+          <t>Kopier e-postene til alle interesserte</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1053" s="22" t="inlineStr">
+        <is>
+          <t>[Button tooltip]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="15" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1054" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.copyEmails</t>
+        </is>
+      </c>
+      <c r="D1054" s="22" t="inlineStr">
+        <is>
+          <t>Copiar E-mails</t>
+        </is>
+      </c>
+      <c r="E1054" s="22" t="inlineStr">
+        <is>
+          <t>Copy Emails</t>
+        </is>
+      </c>
+      <c r="F1054" s="22" t="inlineStr">
+        <is>
+          <t>Kopier E-poster</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1054" s="22" t="inlineStr">
+        <is>
+          <t>[Button label]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="15" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1055" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.exportCsvTooltip</t>
+        </is>
+      </c>
+      <c r="D1055" s="22" t="inlineStr">
+        <is>
+          <t>Baixar planilha (.csv) com os dados dos interessados</t>
+        </is>
+      </c>
+      <c r="E1055" s="22" t="inlineStr">
+        <is>
+          <t>Download spreadsheet (.csv) with interested students data</t>
+        </is>
+      </c>
+      <c r="F1055" s="22" t="inlineStr">
+        <is>
+          <t>Last ned regneark (.csv) med interesserte elevers data</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1055" s="22" t="inlineStr">
+        <is>
+          <t>[Button tooltip]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="15" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1056" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.viewStudents</t>
+        </is>
+      </c>
+      <c r="D1056" s="22" t="inlineStr">
+        <is>
+          <t>Alunos</t>
+        </is>
+      </c>
+      <c r="E1056" s="22" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F1056" s="22" t="inlineStr">
+        <is>
+          <t>Elever</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1056" s="22" t="inlineStr">
+        <is>
+          <t>[Tab label]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="15" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1057" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.interestedStudentsList</t>
+        </is>
+      </c>
+      <c r="D1057" s="22" t="inlineStr">
+        <is>
+          <t>Alunos na Lista de Espera</t>
+        </is>
+      </c>
+      <c r="E1057" s="22" t="inlineStr">
+        <is>
+          <t>Students on Wishlist</t>
+        </is>
+      </c>
+      <c r="F1057" s="22" t="inlineStr">
+        <is>
+          <t>Elever på Ønskeliste</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1057" s="22" t="inlineStr">
+        <is>
+          <t>[Modal header]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="15" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1058" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.removeEntry</t>
+        </is>
+      </c>
+      <c r="D1058" s="22" t="inlineStr">
+        <is>
+          <t>Remover registro</t>
+        </is>
+      </c>
+      <c r="E1058" s="22" t="inlineStr">
+        <is>
+          <t>Remove entry</t>
+        </is>
+      </c>
+      <c r="F1058" s="22" t="inlineStr">
+        <is>
+          <t>Fjern oppføring</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1058" s="22" t="inlineStr">
+        <is>
+          <t>[Action button]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="15" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1059" s="16" t="inlineStr">
+        <is>
+          <t>adminPage</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>adminPage.wishlistManager.confirmDelete</t>
+        </is>
+      </c>
+      <c r="D1059" s="22" t="inlineStr">
+        <is>
+          <t>Deseja remover este registro de interesse da lista?</t>
+        </is>
+      </c>
+      <c r="E1059" s="22" t="inlineStr">
+        <is>
+          <t>Are you sure you want to remove this wish entry?</t>
+        </is>
+      </c>
+      <c r="F1059" s="22" t="inlineStr">
+        <is>
+          <t>Er du sikker på at du vil fjerne denne oppføringen?</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>Completo (3 idiomas) - Revisado nativo</t>
+        </is>
+      </c>
+      <c r="H1059" s="22" t="inlineStr">
+        <is>
+          <t>[Confirmation prompt]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H971"/>

--- a/translations Dance2Dance Ultima versao.xlsx
+++ b/translations Dance2Dance Ultima versao.xlsx
@@ -36480,7 +36480,7 @@
       </c>
       <c r="E979" s="22" t="inlineStr">
         <is>
-          <t>If you have the financial means to pay the standard tuition, your contribution helps keep this opportunity open for those who need it most.</t>
+          <t>If you have the financial means to pay the standard fee, your contribution helps keep this opportunity open for those who need it most.</t>
         </is>
       </c>
       <c r="F979" s="22" t="inlineStr">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="H979" s="22" t="inlineStr">
         <is>
-          <t>[NO: Replaced awkward repetition 'bidrar ditt bidrag' with fluent native structure]</t>
+          <t>[EN: Replaced academic term tuition with standard fee, fitting short-format workshops; NO: fluid native structure]</t>
         </is>
       </c>
     </row>

--- a/translations Dance2Dance Ultima versao.xlsx
+++ b/translations Dance2Dance Ultima versao.xlsx
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D178" s="18" t="inlineStr">
         <is>
-          <t>Erro ao cancelar:</t>
+          <t xml:space="preserve">Erro ao cancelar: </t>
         </is>
       </c>
       <c r="E178" s="18" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="F242" s="18" t="inlineStr">
         <is>
-          <t>Nabolag / Bydel *</t>
+          <t>Nabolag *</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -9499,7 +9499,11 @@
           <t>auth.phonePlaceholder</t>
         </is>
       </c>
-      <c r="D249" s="19" t="n"/>
+      <c r="D249" s="19" t="inlineStr">
+        <is>
+          <t>+55 ... / +47 ...</t>
+        </is>
+      </c>
       <c r="E249" s="19" t="inlineStr">
         <is>
           <t>+47 ...</t>
@@ -11578,12 +11582,12 @@
       </c>
       <c r="E306" s="18" t="inlineStr">
         <is>
-          <t>Automatic habits of movement: which were never chosen: become visible for the first time.</t>
+          <t>Automatic habits of movement - which were never chosen - become visible for the first time.</t>
         </is>
       </c>
       <c r="F306" s="18" t="inlineStr">
         <is>
-          <t>Automatiske bevegelsesvaner: som aldri ble valgt: blir synlige for første gang.</t>
+          <t>Automatiske bevegelsesvaner - som aldri ble valgt - blir synlige for første gang.</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -12947,8 +12951,10 @@
           <t>btd_corporate.pillars_section.pillars[0].number</t>
         </is>
       </c>
-      <c r="D344" s="18" t="n">
-        <v>1</v>
+      <c r="D344" s="18" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="E344" s="18" t="inlineStr">
         <is>
@@ -13233,8 +13239,10 @@
           <t>btd_corporate.pillars_section.pillars[1].number</t>
         </is>
       </c>
-      <c r="D352" s="18" t="n">
-        <v>2</v>
+      <c r="D352" s="18" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
       </c>
       <c r="E352" s="18" t="inlineStr">
         <is>
@@ -13519,8 +13527,10 @@
           <t>btd_corporate.pillars_section.pillars[2].number</t>
         </is>
       </c>
-      <c r="D360" s="18" t="n">
-        <v>3</v>
+      <c r="D360" s="18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
       </c>
       <c r="E360" s="18" t="inlineStr">
         <is>
@@ -14709,7 +14719,11 @@
           <t>contactPage.phonePlaceholder</t>
         </is>
       </c>
-      <c r="D393" s="19" t="n"/>
+      <c r="D393" s="19" t="inlineStr">
+        <is>
+          <t>+55 ... / +47 ...</t>
+        </is>
+      </c>
       <c r="E393" s="19" t="inlineStr">
         <is>
           <t>+47 ...</t>
@@ -16733,8 +16747,10 @@
           <t>corporate.benefits.pillars[0].number</t>
         </is>
       </c>
-      <c r="D449" s="19" t="n">
-        <v>1</v>
+      <c r="D449" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="E449" s="19" t="inlineStr">
         <is>
@@ -17131,8 +17147,10 @@
           <t>corporate.benefits.pillars[1].number</t>
         </is>
       </c>
-      <c r="D460" s="18" t="n">
-        <v>2</v>
+      <c r="D460" s="18" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
       </c>
       <c r="E460" s="18" t="inlineStr">
         <is>
@@ -17533,8 +17551,10 @@
           <t>corporate.benefits.pillars[2].number</t>
         </is>
       </c>
-      <c r="D471" s="19" t="n">
-        <v>3</v>
+      <c r="D471" s="19" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
       </c>
       <c r="E471" s="19" t="inlineStr">
         <is>
@@ -22642,7 +22662,7 @@
       <c r="D611" s="19" t="inlineStr">
         <is>
           <t>[GOLD]Be The Dance. Não apenas dance.
- Seja a dança.</t>
+Seja a dança.</t>
         </is>
       </c>
       <c r="E611" s="19" t="inlineStr">
@@ -24217,9 +24237,9 @@
       <c r="D652" s="18" t="inlineStr">
         <is>
           <t>Encontrar o equilíbrio é aprender a escutar o corpo.
- O equilíbrio não é estático. Está em constante movimento, entre apoio e impulso, estabilidade e mudança, presença e ação.
- Neste workshop, exploramos essa relação dinâmica e as diferentes formas de encontrar estabilidade dentro do movimento. Um convite para descobrir como força, leveza e equilíbrio podem coexistir e criar novas possibilidades.
- O corpo possui uma inteligência própria. Quando aprendemos a escutá-lo, podemos confiar nas suas escolhas e permitir que ele encontre o seu próprio equilíbrio.</t>
+O equilíbrio não é estático. Está em constante movimento, entre apoio e impulso, estabilidade e mudança, presença e ação.
+Neste workshop, exploramos essa relação dinâmica e as diferentes formas de encontrar estabilidade dentro do movimento. Um convite para descobrir como força, leveza e equilíbrio podem coexistir e criar novas possibilidades.
+O corpo possui uma inteligência própria. Quando aprendemos a escutá-lo, podemos confiar nas suas escolhas e permitir que ele encontre o seu próprio equilíbrio.</t>
         </is>
       </c>
       <c r="E652" s="18" t="inlineStr">
@@ -24334,10 +24354,10 @@
       <c r="D655" s="19" t="inlineStr">
         <is>
           <t>Na quietude, o corpo começa a falar.
- Entre um pensamento e outro, entre uma respiração e a seguinte, existe o silêncio. É nesse intervalo que podemos escutar as sensações mais sutis do corpo.
- Neste workshop, exploramos a pausa e a escuta como parte essencial do movimento. Um convite para desacelerar e sentir o corpo, deixando surgir aquilo que se revela quando não há necessidade de estar sempre em movimento.
- A quietude não é ausência de movimento. É sobretudo possibilidade.
- Be Stillness é uma experiência de escuta. Um espaço para estar presente, encontrar o silêncio dentro do movimento e permitir que, a partir dele, a dança se revele.</t>
+Entre um pensamento e outro, entre uma respiração e a seguinte, existe o silêncio. É nesse intervalo que podemos escutar as sensações mais sutis do corpo.
+Neste workshop, exploramos a pausa e a escuta como parte essencial do movimento. Um convite para desacelerar e sentir o corpo, deixando surgir aquilo que se revela quando não há necessidade de estar sempre em movimento.
+A quietude não é ausência de movimento. É sobretudo possibilidade.
+Be Stillness é uma experiência de escuta. Um espaço para estar presente, encontrar o silêncio dentro do movimento e permitir que, a partir dele, a dança se revele.</t>
         </is>
       </c>
       <c r="E655" s="19" t="inlineStr">
@@ -24454,13 +24474,13 @@
       <c r="D658" s="18" t="inlineStr">
         <is>
           <t>Dançar é também encontrar o outro.
- Há músicas que nos fazem viajar, ritmos que despertam o corpo e movimentos que nos aproximam, mesmo quando não falamos a mesma língua.
- Be the Dance Day é um encontro aberto a todos, para dançar, divertir-se e partilhar a experiência do movimento ao som de diferentes músicas e culturas.
- Ao longo do encontro, somos convidados a experimentar diferentes ritmos, formas de dançar e maneiras de nos relacionarmos com a música e com quem está à nossa volta. Sem necessidade de saber dançar, sem passos certos ou errados, apenas a curiosidade de experimentar e a liberdade de nos deixarmos levar.
- Mais do que aprender uma dança, é uma oportunidade para viver a dança como encontro: com a música, com o corpo, com diferentes culturas e com outras pessoas.
- ​
- Be the Dance Day é uma celebração do movimento e da diversidade. Um espaço para soltar o corpo, descobrir novos ritmos, se divertir, criar conexões e simplesmente dançar.
- Venha como você é. Vamos dançar juntos.</t>
+Há músicas que nos fazem viajar, ritmos que despertam o corpo e movimentos que nos aproximam, mesmo quando não falamos a mesma língua.
+Be the Dance Day é um encontro aberto a todos, para dançar, divertir-se e partilhar a experiência do movimento ao som de diferentes músicas e culturas.
+Ao longo do encontro, somos convidados a experimentar diferentes ritmos, formas de dançar e maneiras de nos relacionarmos com a música e com quem está à nossa volta. Sem necessidade de saber dançar, sem passos certos ou errados, apenas a curiosidade de experimentar e a liberdade de nos deixarmos levar.
+Mais do que aprender uma dança, é uma oportunidade para viver a dança como encontro: com a música, com o corpo, com diferentes culturas e com outras pessoas.
+​
+Be the Dance Day é uma celebração do movimento e da diversidade. Um espaço para soltar o corpo, descobrir novos ritmos, se divertir, criar conexões e simplesmente dançar.
+Venha como você é. Vamos dançar juntos.</t>
         </is>
       </c>
       <c r="E658" s="18" t="inlineStr">
@@ -24583,15 +24603,15 @@
       <c r="D661" s="19" t="inlineStr">
         <is>
           <t>Você já é bailarino. Agora, seja a dança.
- A técnica é o instrumento através do qual o bailarino expressa a sua arte. Mas existe algo além dela: uma presença, uma qualidade de entrega, uma forma de estar no movimento que faz com que alguns bailarinos sejam capazes de capturar a nossa atenção e nos tocar de uma maneira única.
- O que é presença?
- Neste workshop, investigamos esse “algo mais”. Um convite para ir além da execução, do intelecto e da mente que observa e controla, e mergulhar numa experiência de presença, consciência e entrega.
- Através de práticas de educação somática, meditação, improvisação guiada e outras ferramentas de exploração do movimento, criamos espaço para escutar o corpo, ampliar a percepção e descobrir novas possibilidades de estar em cena.
- Mais do que acrescentar novas ferramentas à técnica, Be the Dance Pro propõe uma jornada para dentro de si. Uma investigação sobre o que acontece quando deixamos de apenas fazer a dança e permitimos que ela aconteça através de nós.
- O que é carisma?
- ​
- Be the Dance Pro é uma experiência de presença e totalidade. Um espaço para aprofundar a relação entre corpo, mente e movimento e descobrir aquilo que torna cada bailarino único. Uma busca por se perder na dança para encontrar aquele lugar onde bailarino e dança deixam de ser duas coisas diferentes.
- O momento em que o bailarino é a própria dança.</t>
+A técnica é o instrumento através do qual o bailarino expressa a sua arte. Mas existe algo além dela: uma presença, uma qualidade de entrega, uma forma de estar no movimento que faz com que alguns bailarinos sejam capazes de capturar a nossa atenção e nos tocar de uma maneira única.
+O que é presença?
+Neste workshop, investigamos esse “algo mais”. Um convite para ir além da execução, do intelecto e da mente que observa e controla, e mergulhar numa experiência de presença, consciência e entrega.
+Através de práticas de educação somática, meditação, improvisação guiada e outras ferramentas de exploração do movimento, criamos espaço para escutar o corpo, ampliar a percepção e descobrir novas possibilidades de estar em cena.
+Mais do que acrescentar novas ferramentas à técnica, Be the Dance Pro propõe uma jornada para dentro de si. Uma investigação sobre o que acontece quando deixamos de apenas fazer a dança e permitimos que ela aconteça através de nós.
+O que é carisma?
+​
+Be the Dance Pro é uma experiência de presença e totalidade. Um espaço para aprofundar a relação entre corpo, mente e movimento e descobrir aquilo que torna cada bailarino único. Uma busca por se perder na dança para encontrar aquele lugar onde bailarino e dança deixam de ser duas coisas diferentes.
+O momento em que o bailarino é a própria dança.</t>
         </is>
       </c>
       <c r="E661" s="19" t="inlineStr">
@@ -24790,10 +24810,10 @@
       <c r="D666" s="18" t="inlineStr">
         <is>
           <t>Dançar é ser inteiro. É não guardar nada.
- Sem se proteger, sem hesitar, sem guardar energia. Quando nos permitimos estar por inteiro no que fazemos, o corpo encontra liberdade para se expressar com espontaneidade e verdade.
- Neste workshop, exploramos a entrega total ao momento. Um convite para confiar no impulso, comprometer-se plenamente com cada gesto e deixar que o corpo se expresse sem reservas.
- Não se trata de fazer mais, mas de estar completamente presente no que fazemos. De colocar tudo no movimento e permitir que cada gesto seja vivido por inteiro.
- Be Total é uma experiência de entrega e expressão. Um espaço para estar totalmente presente, sem poupar energia e descobrir o que acontece quando nos permitimos dançar sem reservas.</t>
+Sem se proteger, sem hesitar, sem guardar energia. Quando nos permitimos estar por inteiro no que fazemos, o corpo encontra liberdade para se expressar com espontaneidade e verdade.
+Neste workshop, exploramos a entrega total ao momento. Um convite para confiar no impulso, comprometer-se plenamente com cada gesto e deixar que o corpo se expresse sem reservas.
+Não se trata de fazer mais, mas de estar completamente presente no que fazemos. De colocar tudo no movimento e permitir que cada gesto seja vivido por inteiro.
+Be Total é uma experiência de entrega e expressão. Um espaço para estar totalmente presente, sem poupar energia e descobrir o que acontece quando nos permitimos dançar sem reservas.</t>
         </is>
       </c>
       <c r="E666" s="18" t="inlineStr">
@@ -24982,10 +25002,10 @@
       <c r="D671" s="19" t="inlineStr">
         <is>
           <t>Entregar-se ao movimento é encontrar o fluxo.
- Quando deixamos de tentar conduzir cada gesto, o corpo encontra naturalmente novos caminhos. O movimento torna-se mais livre e orgânico, guiado pela escuta e pela sensação.
- Neste workshop, exploramos o fluir como possibilidade de expressão. Um convite para experimentar o movimento sem resistência, confiar no corpo e permitir que uma ação conduza naturalmente à seguinte.
- Como a água, que encontra o seu caminho sem precisar lutar contra ele, aprendemos a acompanhar o movimento em vez de controlá-lo.
- Be Water é uma experiência de entrega. Um espaço para deixar o corpo seguir o seu próprio fluxo e descobrir a dança que surge quando simplesmente nos deixamos levar.</t>
+Quando deixamos de tentar conduzir cada gesto, o corpo encontra naturalmente novos caminhos. O movimento torna-se mais livre e orgânico, guiado pela escuta e pela sensação.
+Neste workshop, exploramos o fluir como possibilidade de expressão. Um convite para experimentar o movimento sem resistência, confiar no corpo e permitir que uma ação conduza naturalmente à seguinte.
+Como a água, que encontra o seu caminho sem precisar lutar contra ele, aprendemos a acompanhar o movimento em vez de controlá-lo.
+Be Water é uma experiência de entrega. Um espaço para deixar o corpo seguir o seu próprio fluxo e descobrir a dança que surge quando simplesmente nos deixamos levar.</t>
         </is>
       </c>
       <c r="E671" s="19" t="inlineStr">
@@ -25826,7 +25846,7 @@
       <c r="D694" s="18" t="inlineStr">
         <is>
           <t>Talvez você tenha passado a vida inteira tentando fazer seu corpo obedecer.
- E se agora fosse o momento de escutá-lo? É essa investigação que proponho nas aulas de Biostretch. Um convite para desacelerar, para sentir, para respirar. Para soltar o que já não precisa ser sustentado. Para descobrir caminhos que estavam ali o tempo todo, esperando apenas que você prestasse atenção.</t>
+E se agora fosse o momento de escutá-lo? É essa investigação que proponho nas aulas de Biostretch. Um convite para desacelerar, para sentir, para respirar. Para soltar o que já não precisa ser sustentado. Para descobrir caminhos que estavam ali o tempo todo, esperando apenas que você prestasse atenção.</t>
         </is>
       </c>
       <c r="E694" s="18" t="inlineStr">
@@ -27309,11 +27329,11 @@
       <c r="D733" s="19" t="inlineStr">
         <is>
           <t>Estamos quase sempre ocupados com alguma coisa. Mas estar ocupado não significa, necessariamente, estar presente.
- Nosso corpo e nossa mente se acostumaram ao movimento, à ação e aos estímulos constantes. Por isso, simplesmente sentar, ficar em silêncio e estar presente pode ser um desafio.
- Vamos primeiro criar condições para que o corpo encontre conforto e quietude.
- No workshop Alongar, Respirar e Meditar, vamos explorar movimentos suaves para liberar as articulações e tensões desnecessárias. Vamos buscar pontos de apoio que nos permitam sentar com mais conforto e estabilidade, mantendo a coluna ereta sem rigidez.
- A respiração será nossa âncora enquanto o corpo e a mente desaceleram. Sem forçar. Sem tentar alcançar mais do que o corpo permite, apenas percebendo como o corpo está no momento.
- Sem precisar alcançar nada. Sem precisar fazer nada. Apenas criando espaço para a meditação acontecer.</t>
+Nosso corpo e nossa mente se acostumaram ao movimento, à ação e aos estímulos constantes. Por isso, simplesmente sentar, ficar em silêncio e estar presente pode ser um desafio.
+Vamos primeiro criar condições para que o corpo encontre conforto e quietude.
+No workshop Alongar, Respirar e Meditar, vamos explorar movimentos suaves para liberar as articulações e tensões desnecessárias. Vamos buscar pontos de apoio que nos permitam sentar com mais conforto e estabilidade, mantendo a coluna ereta sem rigidez.
+A respiração será nossa âncora enquanto o corpo e a mente desaceleram. Sem forçar. Sem tentar alcançar mais do que o corpo permite, apenas percebendo como o corpo está no momento.
+Sem precisar alcançar nada. Sem precisar fazer nada. Apenas criando espaço para a meditação acontecer.</t>
         </is>
       </c>
       <c r="E733" s="19" t="inlineStr">
@@ -27432,11 +27452,11 @@
       <c r="D736" s="18" t="inlineStr">
         <is>
           <t>Estar relaxado é nosso estado natural. Por isso, relaxar não é algo que possamos fazer, mas sim algo que podemos deixar acontecer liberando tensões e esforços que já não são necessários.
- Quando o corpo se sente seguro e confortável, o relaxamento acontece naturalmente e podemos perceber melhor nossa respiração, nossos movimentos e os hábitos que influenciam a maneira como nos relacionamos com o próprio corpo.
- ​
- No workshop Aprendendo a Relaxar, através de movimentos suaves e sem esforço, conectados com a respiração, vamos criar condições para que o corpo desacelere e o sistema nervoso encontre um estado de maior calma e restauração.
- O relaxamento se torna, então, muito mais do que uma pausa. Ele pode ser um caminho para ampliar a consciência, perceber o que acontece dentro de nós e descobrir novas possibilidades de estar no mundo.
- Mais calma por dentro. Mais presença, confiança e liberdade para encontrar o mundo lá fora.</t>
+Quando o corpo se sente seguro e confortável, o relaxamento acontece naturalmente e podemos perceber melhor nossa respiração, nossos movimentos e os hábitos que influenciam a maneira como nos relacionamos com o próprio corpo.
+​
+No workshop Aprendendo a Relaxar, através de movimentos suaves e sem esforço, conectados com a respiração, vamos criar condições para que o corpo desacelere e o sistema nervoso encontre um estado de maior calma e restauração.
+O relaxamento se torna, então, muito mais do que uma pausa. Ele pode ser um caminho para ampliar a consciência, perceber o que acontece dentro de nós e descobrir novas possibilidades de estar no mundo.
+Mais calma por dentro. Mais presença, confiança e liberdade para encontrar o mundo lá fora.</t>
         </is>
       </c>
       <c r="E736" s="18" t="inlineStr">
@@ -27555,10 +27575,10 @@
       <c r="D739" s="19" t="inlineStr">
         <is>
           <t>O estresse é uma resposta natural do nosso organismo diante de situações que exigem adaptação.
- A maneira como o nosso corpo responde ao estresse e retorna a um estado de equilíbrio, influencia nosso bem estar. Podemos permanecer por longos períodos acumulando tensão e esforço sem perceber. Com o tempo, isso pode afetar nossa energia, concentração, nosso sono, a capacidade de relaxar e nossa qualidade de vida.
- No workshop Movimentos Diários para Prevenir o Estresse, vamos explorar movimentos que ajudam a perceber e liberar tensões acumuladas e direcionar a atenção para regiões do corpo que tendemos a manter contraídas.
- Mais do que relaxar por alguns momentos, vamos aprender movimentos e estratégias simples que podem ser incorporados ao cotidiano, criando pequenas pausas para interromper o acúmulo de tensão e recuperar o equilíbrio.
- Aprender a perceber o estresse no corpo é o primeiro passo para aprender a responder a ele de uma maneira diferente.</t>
+A maneira como o nosso corpo responde ao estresse e retorna a um estado de equilíbrio, influencia nosso bem estar. Podemos permanecer por longos períodos acumulando tensão e esforço sem perceber. Com o tempo, isso pode afetar nossa energia, concentração, nosso sono, a capacidade de relaxar e nossa qualidade de vida.
+No workshop Movimentos Diários para Prevenir o Estresse, vamos explorar movimentos que ajudam a perceber e liberar tensões acumuladas e direcionar a atenção para regiões do corpo que tendemos a manter contraídas.
+Mais do que relaxar por alguns momentos, vamos aprender movimentos e estratégias simples que podem ser incorporados ao cotidiano, criando pequenas pausas para interromper o acúmulo de tensão e recuperar o equilíbrio.
+Aprender a perceber o estresse no corpo é o primeiro passo para aprender a responder a ele de uma maneira diferente.</t>
         </is>
       </c>
       <c r="E739" s="19" t="inlineStr">
@@ -27675,12 +27695,12 @@
       <c r="D742" s="18" t="inlineStr">
         <is>
           <t>Nosso foco está sendo roubado. Notificações, redes sociais, e-mails, multitarefas. Vivemos sob uma avalanche constante de informações que fragmenta nossa atenção e nos afasta do momento presente.
- Diante disso, é natural tentar recuperar a concentração com mais esforço: mais disciplina, mais controle, mais força de vontade. Mas a mente já está sobrecarregada. Exigir mais dela é como tentar esvaziar um copo cheio enchendo-o ainda mais.
- O caminho é inverso.
- Para recuperar a capacidade de foco, precisamos primeiro nos esvaziar. Liberar o acúmulo de tensão, de estímulos e de ruído que o corpo e a mente carregam sem perceber.
- No workshop Recuperando o Foco, vamos usar movimentos suaves e sem esforço para criar um espaço interno de silêncio e segurança. Ao direcionar a atenção para o corpo e para a respiração, permitimos que o sistema nervoso desacelere e que a mente encontre, naturalmente, um estado de maior clareza.
- Não se trata de treinar a concentração. Se trata de criar as condições para que ela se restaure por si mesma. Quando o corpo relaxa e a mente se esvazia, o foco ressurge como consequência de um estado de presença.
- Recuperar o foco é, antes de tudo, recuperar a quietude.</t>
+Diante disso, é natural tentar recuperar a concentração com mais esforço: mais disciplina, mais controle, mais força de vontade. Mas a mente já está sobrecarregada. Exigir mais dela é como tentar esvaziar um copo cheio enchendo-o ainda mais.
+O caminho é inverso.
+Para recuperar a capacidade de foco, precisamos primeiro nos esvaziar. Liberar o acúmulo de tensão, de estímulos e de ruído que o corpo e a mente carregam sem perceber.
+No workshop Recuperando o Foco, vamos usar movimentos suaves e sem esforço para criar um espaço interno de silêncio e segurança. Ao direcionar a atenção para o corpo e para a respiração, permitimos que o sistema nervoso desacelere e que a mente encontre, naturalmente, um estado de maior clareza.
+Não se trata de treinar a concentração. Se trata de criar as condições para que ela se restaure por si mesma. Quando o corpo relaxa e a mente se esvazia, o foco ressurge como consequência de um estado de presença.
+Recuperar o foco é, antes de tudo, recuperar a quietude.</t>
         </is>
       </c>
       <c r="E742" s="18" t="inlineStr">
@@ -27801,10 +27821,10 @@
       <c r="D745" s="19" t="inlineStr">
         <is>
           <t>Grande parte do que fazemos todos os dias acontece automaticamente. São hábitos e padrões de movimento que aprendemos ao longo da vida e que influenciam nossa postura, a maneira como nos movemos e até como nos sentimos.
- Os hábitos são importantes. Com eles, é possível realizar tarefas sem precisar reaprender a fazê-las a cada vez. Mas alguns padrões que um dia foram úteis podem, com o tempo, tornar-se limitantes, criando tensões, desconfortos e esforços desnecessários.
- No workshop Transformando Hábitos, vamos reconhecer esses padrões e experimentar novas possibilidades de movimento. Ao ampliar nossa percepção, surgem novos caminhos de movimento antes nunca usados.
- Um hábito não precisa simplesmente ser eliminado. Podemos transformá-lo, oferecendo ao corpo novas opções e permitindo que ele descubra maneiras mais fáceis, prazerosas e eficientes de se mover.
- Mais percepção. Mais possibilidades. Mais liberdade para escolher como se mover.</t>
+Os hábitos são importantes. Com eles, é possível realizar tarefas sem precisar reaprender a fazê-las a cada vez. Mas alguns padrões que um dia foram úteis podem, com o tempo, tornar-se limitantes, criando tensões, desconfortos e esforços desnecessários.
+No workshop Transformando Hábitos, vamos reconhecer esses padrões e experimentar novas possibilidades de movimento. Ao ampliar nossa percepção, surgem novos caminhos de movimento antes nunca usados.
+Um hábito não precisa simplesmente ser eliminado. Podemos transformá-lo, oferecendo ao corpo novas opções e permitindo que ele descubra maneiras mais fáceis, prazerosas e eficientes de se mover.
+Mais percepção. Mais possibilidades. Mais liberdade para escolher como se mover.</t>
         </is>
       </c>
       <c r="E745" s="19" t="inlineStr">
@@ -27921,12 +27941,12 @@
       <c r="D748" s="18" t="inlineStr">
         <is>
           <t>Sua postura conta uma história. Ela reflete a maneira como você organiza o corpo, os hábitos que desenvolveu ao longo da vida e a forma como se relaciona com o ambiente ao seu redor.
- Mais do que uma posição que devemos manter, a postura é uma organização dinâmica do corpo para se mover, se equilibrar e encontrar o mundo. Ela está presente em tudo o que fazemos e influencia nossa sensação de conforto, liberdade de movimento, apoio e bem-estar.
- Nosso esqueleto e nossa musculatura possuem uma incrível capacidade de nos sustentar contra a gravidade e, ao mesmo tempo, permitir movimento e adaptação. Porém, ao longo do tempo, podemos desenvolver hábitos que aumentam o esforço necessário para nos manter de pé e nos mover, criando tensão, desconforto e limitações desnecessárias.
- A postura não é, portanto, algo estático nem uma “posição correta” que precisamos controlar o tempo todo. As diferentes partes do corpo estão constantemente se relacionando e ajustando entre si. Existe uma conversa contínua entre músculos, ossos, respiração, equilíbrio e movimento.
- É essa inteligência inata do corpo que nos permite encontrar equilíbrio e suporte.
- No workshop Uma Melhor Postura, você terá a oportunidade de reconhecer padrões posturais habituais e explorar novas possibilidades de organização do corpo. Através da percepção e do movimento, podemos reduzir esforços desnecessários e descobrir maneiras mais eficazes, confortáveis e naturais de nos sustentar.
- Uma postura saudável não é rígida. Ela é estável e, ao mesmo tempo, flexível. É a sensação de estar apoiado, de encontrar a verticalidade sem esforço excessivo e de poder se mover com mais facilidade, liberdade e presença.</t>
+Mais do que uma posição que devemos manter, a postura é uma organização dinâmica do corpo para se mover, se equilibrar e encontrar o mundo. Ela está presente em tudo o que fazemos e influencia nossa sensação de conforto, liberdade de movimento, apoio e bem-estar.
+Nosso esqueleto e nossa musculatura possuem uma incrível capacidade de nos sustentar contra a gravidade e, ao mesmo tempo, permitir movimento e adaptação. Porém, ao longo do tempo, podemos desenvolver hábitos que aumentam o esforço necessário para nos manter de pé e nos mover, criando tensão, desconforto e limitações desnecessárias.
+A postura não é, portanto, algo estático nem uma “posição correta” que precisamos controlar o tempo todo. As diferentes partes do corpo estão constantemente se relacionando e ajustando entre si. Existe uma conversa contínua entre músculos, ossos, respiração, equilíbrio e movimento.
+É essa inteligência inata do corpo que nos permite encontrar equilíbrio e suporte.
+No workshop Uma Melhor Postura, você terá a oportunidade de reconhecer padrões posturais habituais e explorar novas possibilidades de organização do corpo. Através da percepção e do movimento, podemos reduzir esforços desnecessários e descobrir maneiras mais eficazes, confortáveis e naturais de nos sustentar.
+Uma postura saudável não é rígida. Ela é estável e, ao mesmo tempo, flexível. É a sensação de estar apoiado, de encontrar a verticalidade sem esforço excessivo e de poder se mover com mais facilidade, liberdade e presença.</t>
         </is>
       </c>
       <c r="E748" s="18" t="inlineStr">
@@ -28486,9 +28506,9 @@
           <t>programs.kroppsskole.subtitle</t>
         </is>
       </c>
-      <c r="D763" s="19" t="n"/>
-      <c r="E763" s="19" t="n"/>
-      <c r="F763" s="19" t="n"/>
+      <c r="D763" s="19" t="inlineStr"/>
+      <c r="E763" s="19" t="inlineStr"/>
+      <c r="F763" s="19" t="inlineStr"/>
       <c r="G763" s="11" t="inlineStr">
         <is>
           <t>Completo (3 idiomas) - Revisado nativo</t>
@@ -29349,7 +29369,7 @@
       <c r="D787" s="19" t="inlineStr">
         <is>
           <t>Porque o corpo não precisa apenas de estímulo.
- Precisa de tempo para aprender.</t>
+Precisa de tempo para aprender.</t>
         </is>
       </c>
       <c r="E787" s="19" t="inlineStr">
@@ -30655,17 +30675,17 @@
       </c>
       <c r="D823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo é um bairro de contrastes: diversidade, história e riqueza cultural convivem com desigualdades de acesso a serviços e atividades de qualidade. É exatamente esse contexto que nos chama a agir.</t>
+          <t>Tøyen e Grønland são bairros de contrastes - diversidade, história e riqueza cultural convivem com desigualdades de acesso a serviços e atividades de qualidade. É exatamente esse contexto que nos chama a agir.</t>
         </is>
       </c>
       <c r="E823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo is a neighbourhood of contrasts: diversity, history and cultural richness coexist with inequalities in access to quality services and activities. This is exactly the context that calls us to act.</t>
+          <t>Tøyen and Grønland are neighbourhoods of contrast - diversity, history and cultural richness coexist with inequalities in access to quality services and activities. This is exactly the context that calls us to act.</t>
         </is>
       </c>
       <c r="F823" s="19" t="inlineStr">
         <is>
-          <t>Gamle Oslo er et nabolag fylt av kontraster: mangfold, historie og kulturell rikdom eksisterer side om side med ulikhet i tilgang til kvalitetstjenester og aktiviteter. Det er nettopp denne virkeligheten som kaller oss til handling.</t>
+          <t>Tøyen og Grønland er nabolag fylt av kontraster - mangfold, historie og kulturell rikdom eksisterer side om side med ulikhet i tilgang til kvalitetstjenester og aktiviteter. Det er nettopp denne virkeligheten som kaller oss til handling.</t>
         </is>
       </c>
       <c r="G823" s="9" t="inlineStr">
@@ -30695,17 +30715,17 @@
       </c>
       <c r="D824" s="18" t="inlineStr">
         <is>
-          <t>O Dance2Dance nasce nesse território com uma missão clara: que a dança, a expressão corporal e o bem-estar não sejam privilégio de quem pode pagar. Cada workshop que desenvolvemos tem a mesma qualidade, o mesmo cuidado e a mesma intenção: independentemente de quem está na sala.</t>
+          <t>O Dance2Dance nasce nesse território com uma missão clara: que a dança, a expressão corporal e o bem-estar não sejam privilégio de quem pode pagar. Cada workshop que desenvolvemos tem a mesma qualidade, o mesmo cuidado e a mesma intenção - independentemente de quem está na sala.</t>
         </is>
       </c>
       <c r="E824" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance is born in this territory with a clear mission: that dance, movement and well-being should not be a privilege for those who can pay. Every workshop we develop carries the same quality, the same care and the same intention: regardless of who is in the room.</t>
+          <t>Dance2Dance is born in this territory with a clear mission: that dance, movement and well-being should not be a privilege for those who can pay. Every workshop we develop carries the same quality, the same care and the same intention - regardless of who is in the room.</t>
         </is>
       </c>
       <c r="F824" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance fødes i dette territoriet med et tydelig oppdrag: at dans, kroppsuttrykk og velvære ikke skal være et privilegium for dem som kan betale. Hver workshop vi utvikler har samme kvalitet, samme omsorg og samme intensjon: uavhengig av hvem som er i rommet.</t>
+          <t>Dance2Dance fødes i dette territoriet med et tydelig oppdrag: at dans, kroppsuttrykk og velvære ikke skal være et privilegium for dem som kan betale. Hver workshop vi utvikler har samme kvalitet, samme omsorg og samme intensjon - uavhengig av hvem som er i rommet.</t>
         </is>
       </c>
       <c r="G824" s="5" t="inlineStr">
@@ -30771,17 +30791,17 @@
       </c>
       <c r="D826" s="18" t="inlineStr">
         <is>
-          <t>Por que Gamle Oslo?</t>
+          <t>Por que Tøyen e Grønland?</t>
         </is>
       </c>
       <c r="E826" s="18" t="inlineStr">
         <is>
-          <t>Why Gamle Oslo?</t>
+          <t>Why Tøyen and Grønland?</t>
         </is>
       </c>
       <c r="F826" s="18" t="inlineStr">
         <is>
-          <t>Hvorfor Gamle Oslo?</t>
+          <t>Hvorfor Tøyen og Grønland?</t>
         </is>
       </c>
       <c r="G826" s="5" t="inlineStr">
@@ -30879,17 +30899,17 @@
       </c>
       <c r="D829" s="19" t="inlineStr">
         <is>
-          <t>Fundos, empresas e parceiros que chegam agora são parte da fundação: e da história: deste projeto. Entre em contato e descubra como fazer parte.</t>
+          <t>Fundos, empresas e parceiros que chegam agora são parte da fundação - e da história - deste projeto. Entre em contato e descubra como fazer parte.</t>
         </is>
       </c>
       <c r="E829" s="19" t="inlineStr">
         <is>
-          <t>Funds, companies and partners who arrive now are part of the foundation: and the story: of this project. Get in touch and discover how to be part of it.</t>
+          <t>Funds, companies and partners who arrive now are part of the foundation - and the story - of this project. Get in touch and discover how to be part of it.</t>
         </is>
       </c>
       <c r="F829" s="19" t="inlineStr">
         <is>
-          <t>Fond, bedrifter og partnere som kommer nå er en del av grunnlaget: og historien: til dette prosjektet. Ta kontakt og finn ut hvordan du kan være en del av det.</t>
+          <t>Fond, bedrifter og partnere som kommer nå er en del av grunnlaget - og historien - til dette prosjektet. Ta kontakt og finn ut hvordan du kan være en del av det.</t>
         </is>
       </c>
       <c r="G829" s="9" t="inlineStr">
@@ -31059,17 +31079,17 @@
       </c>
       <c r="D834" s="18" t="inlineStr">
         <is>
-          <t>Um modelo de acesso universal à cultura e ao movimento. Workshops de alto nível, gratuitos para moradores de Gamle Oslo: sustentados por múltiplas fontes de financiamento.</t>
+          <t>Um modelo de acesso universal à cultura e ao movimento. Workshops de alto nível, gratuitos para moradores de Tøyen e Grønland - sustentados por múltiplas fontes de financiamento.</t>
         </is>
       </c>
       <c r="E834" s="18" t="inlineStr">
         <is>
-          <t>A model for universal access to culture and movement. Premium workshops, free for residents of Gamle Oslo: sustained by multiple funding sources.</t>
+          <t>A model for universal access to culture and movement. Premium workshops, free for residents of Tøyen and Grønland - sustained by multiple funding sources.</t>
         </is>
       </c>
       <c r="F834" s="18" t="inlineStr">
         <is>
-          <t>En modell for universell tilgang til kultur og bevegelse. Premium workshops, gratis for beboere i Gamle Oslo: båret av flere finansieringskilder.</t>
+          <t>En modell for universell tilgang til kultur og bevegelse. Premium workshops, gratis for beboere i Tøyen og Grønland - båret av flere finansieringskilder.</t>
         </is>
       </c>
       <c r="G834" s="5" t="inlineStr">
@@ -31207,17 +31227,17 @@
       </c>
       <c r="D838" s="18" t="inlineStr">
         <is>
-          <t>O Dance2Dance foi desenhado para não depender de uma única fonte. Nossa sustentabilidade nasce da combinação estratégica de múltiplos pilares: cada um essencial, nenhum suficiente sozinho.</t>
+          <t>O Dance2Dance foi desenhado para não depender de uma única fonte. Nossa sustentabilidade nasce da combinação estratégica de múltiplos pilares - cada um essencial, nenhum suficiente sozinho.</t>
         </is>
       </c>
       <c r="E838" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance was designed not to rely on a single source. Our sustainability comes from the strategic combination of multiple pillars: each essential, none sufficient alone.</t>
+          <t>Dance2Dance was designed not to rely on a single source. Our sustainability comes from the strategic combination of multiple pillars - each essential, none sufficient alone.</t>
         </is>
       </c>
       <c r="F838" s="18" t="inlineStr">
         <is>
-          <t>Dance2Dance er designet for å ikke stole på en enkelt kilde. Vår bærekraft kommer fra den strategiske kombinasjonen av flere pilarer: hver enkelt essensiell, ingen tilstrekkelig alene.</t>
+          <t>Dance2Dance er designet for å ikke stole på en enkelt kilde. Vår bærekraft kommer fra den strategiske kombinasjonen av flere pilarer - hver enkelt essensiell, ingen tilstrekkelig alene.</t>
         </is>
       </c>
       <c r="G838" s="5" t="inlineStr">
@@ -31283,17 +31303,17 @@
       </c>
       <c r="D840" s="18" t="inlineStr">
         <is>
-          <t>Quem vem de fora de Gamle Oslo paga o valor real do workshop. Essa receita contribui diretamente para viabilizar o acesso gratuito aos moradores locais.</t>
+          <t>Quem vem de fora de Tøyen e Grønland paga o valor real do workshop. Essa receita contribui diretamente para viabilizar o acesso gratuito aos moradores locais.</t>
         </is>
       </c>
       <c r="E840" s="18" t="inlineStr">
         <is>
-          <t>Those who come from outside Gamle Oslo pay the real value of the workshop. This revenue directly contributes to enabling free access for local residents.</t>
+          <t>Those who come from outside Tøyen and Grønland pay the real value of the workshop. This revenue directly contributes to enabling free access for local residents.</t>
         </is>
       </c>
       <c r="F840" s="18" t="inlineStr">
         <is>
-          <t>De som kommer fra utenfor Gamle Oslo betaler den reelle verdien av workshopen. Denne inntekten bidrar direkte til å muliggjøre gratis tilgang for lokale beboere.</t>
+          <t>De som kommer fra utenfor Tøyen og Grønland betaler den reelle verdien av workshopen. Denne inntekten bidrar direkte til å muliggjøre gratis tilgang for lokale beboere.</t>
         </is>
       </c>
       <c r="G840" s="5" t="inlineStr">
@@ -31787,17 +31807,17 @@
       </c>
       <c r="D854" s="18" t="inlineStr">
         <is>
-          <t>Moradores de Gamle Oslo</t>
+          <t>Moradores de Tøyen e Grønland</t>
         </is>
       </c>
       <c r="E854" s="18" t="inlineStr">
         <is>
-          <t>Gamle Oslo residents</t>
+          <t>Tøyen and Grønland residents</t>
         </is>
       </c>
       <c r="F854" s="18" t="inlineStr">
         <is>
-          <t>Beboere i Gamle Oslo</t>
+          <t>Beboere i Tøyen og Grønland</t>
         </is>
       </c>
       <c r="G854" s="5" t="inlineStr">
@@ -31859,17 +31879,17 @@
       </c>
       <c r="D856" s="18" t="inlineStr">
         <is>
-          <t>“O acesso gratuito com transparência de preço cria dignidade. A pessoa não recebe caridade: recebe a oportunidade de participar de algo que tem valor real.”</t>
+          <t>“O acesso gratuito com transparência de preço cria dignidade. A pessoa não recebe caridade - recebe a oportunidade de participar de algo que tem valor real.”</t>
         </is>
       </c>
       <c r="E856" s="18" t="inlineStr">
         <is>
-          <t>“Free access with price transparency creates dignity. The person is not receiving charity: they are receiving the opportunity to be part of something with real value.”</t>
+          <t>“Free access with price transparency creates dignity. The person is not receiving charity - they are receiving the opportunity to be part of something with real value.”</t>
         </is>
       </c>
       <c r="F856" s="18" t="inlineStr">
         <is>
-          <t>“Gratis tilgang med pristransparens skaper verdighet. Personen mottar ikke veldedighet: de mottar muligheten til å være en del av noe med ekte verdi.”</t>
+          <t>“Gratis tilgang med pristransparens skaper verdighet. Personen mottar ikke veldedighet - de mottar muligheten til å være en del av noe med ekte verdi.”</t>
         </is>
       </c>
       <c r="G856" s="5" t="inlineStr">
@@ -31931,17 +31951,17 @@
       </c>
       <c r="D858" s="18" t="inlineStr">
         <is>
-          <t>Moradores de fora de Gamle Oslo participam mediante pagamento regular, com acesso à mesma experiência de qualidade premium.</t>
+          <t>Moradores de fora de Tøyen e Grønland participam mediante pagamento regular, com acesso à mesma experiência de qualidade premium.</t>
         </is>
       </c>
       <c r="E858" s="18" t="inlineStr">
         <is>
-          <t>Residents from outside Gamle Oslo participate at the regular rate, with access to the same premium quality experience.</t>
+          <t>Residents from outside Tøyen and Grønland participate at the regular rate, with access to the same premium quality experience.</t>
         </is>
       </c>
       <c r="F858" s="18" t="inlineStr">
         <is>
-          <t>Beboere utenfor Gamle Oslo deltar til vanlig pris, med tilgang til den samme premium-opplevelsen.</t>
+          <t>Beboere utenfor Tøyen og Grønland deltar til vanlig pris, med tilgang til den samme premium-opplevelsen.</t>
         </is>
       </c>
       <c r="G858" s="5" t="inlineStr">
@@ -32039,17 +32059,17 @@
       </c>
       <c r="D861" s="19" t="inlineStr">
         <is>
-          <t>Quem recebe gratuitamente recebe exatamente o mesmo que quem paga. Tornamos o preço real visível porque valor percebido importa: tanto para quem apia quanto para quem participa.</t>
+          <t>Quem recebe gratuitamente recebe exatamente o mesmo que quem paga. Tornamos o preço real visível porque valor percebido importa - tanto para quem apia quanto para quem participa.</t>
         </is>
       </c>
       <c r="E861" s="19" t="inlineStr">
         <is>
-          <t>Those who receive it for free receive exactly the same as those who pay. We make the real price visible because perceived value matters: for supporters and participants alike.</t>
+          <t>Those who receive it for free receive exactly the same as those who pay. We make the real price visible because perceived value matters - for supporters and participants alike.</t>
         </is>
       </c>
       <c r="F861" s="19" t="inlineStr">
         <is>
-          <t>De som mottar det gratis, mottar nøyaktig det samme som de som betaler. Vi gjør den reelle prisen synlig fordi opplevd verdi betyr noe: både for støttespillere og deltakere.</t>
+          <t>De som mottar det gratis, mottar nøyaktig det samme som de som betaler. Vi gjør den reelle prisen synlig fordi opplevd verdi betyr noe - både for støttespillere og deltakere.</t>
         </is>
       </c>
       <c r="G861" s="9" t="inlineStr">
